--- a/outputs/reports/comparison/leakage_audit.xlsx
+++ b/outputs/reports/comparison/leakage_audit.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003524344080407258</v>
+        <v>0.003245465363672425</v>
       </c>
     </row>
     <row r="4">
@@ -615,17 +615,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6002721805751534</v>
+        <v>0.5953456177723242</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004708441933972957</v>
+        <v>0.004388227477903696</v>
       </c>
       <c r="D2" t="n">
-        <v>1.335976802080253</v>
+        <v>1.352110402108304</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -634,17 +634,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5995989233663561</v>
+        <v>0.5865129899625758</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004949717107667742</v>
+        <v>0.00451154947971646</v>
       </c>
       <c r="D3" t="n">
-        <v>1.404436398586762</v>
+        <v>1.390108651355746</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -653,17 +653,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5879865329877604</v>
+        <v>0.5665283492279621</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004869831697776494</v>
+        <v>0.003816934440223919</v>
       </c>
       <c r="D4" t="n">
-        <v>1.381769653209842</v>
+        <v>1.176082321798328</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -672,17 +672,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5720432544972825</v>
+        <v>0.5639898417659797</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004177731291802433</v>
+        <v>0.004020446872672561</v>
       </c>
       <c r="D5" t="n">
-        <v>1.185392571351794</v>
+        <v>1.238789024734253</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5695308533094522</v>
+        <v>0.5635780338585543</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004157854484549757</v>
+        <v>0.003781455584011756</v>
       </c>
       <c r="D6" t="n">
-        <v>1.179752711338359</v>
+        <v>1.165150497780333</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -710,17 +710,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_CNT</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5515215312382313</v>
+        <v>0.5598697291247227</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004222963153746261</v>
+        <v>0.003659745890894433</v>
       </c>
       <c r="D7" t="n">
-        <v>1.198226693364819</v>
+        <v>1.127649036671039</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5509794731651845</v>
+        <v>0.55683852371723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005074429925820346</v>
+        <v>0.005400036456637725</v>
       </c>
       <c r="D8" t="n">
-        <v>1.439822505989247</v>
+        <v>1.663871233100231</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -748,17 +748,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_AMT</t>
+          <t>CUMU_PYHWY_EXE_CNT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5479883470590321</v>
+        <v>0.5476144328059797</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003944788949098847</v>
+        <v>0.003792557774419537</v>
       </c>
       <c r="D9" t="n">
-        <v>1.119297338483195</v>
+        <v>1.168571329360313</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -767,17 +767,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>OPCT_YN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5459608255722007</v>
+        <v>0.5464846449371249</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004217327398685448</v>
+        <v>0.003663743761293497</v>
       </c>
       <c r="D10" t="n">
-        <v>1.19662760004923</v>
+        <v>1.128880869382555</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -786,17 +786,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LBST_EXE_CNT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5446400785061156</v>
+        <v>0.5444679008528904</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003949814166933189</v>
+        <v>0.00369384421156972</v>
       </c>
       <c r="D11" t="n">
-        <v>1.120723197513895</v>
+        <v>1.138155487011554</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,17 +805,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LBST_EXE_CNT</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5398779406682276</v>
+        <v>0.5435407363211828</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003934539347408408</v>
+        <v>0.003560921462815187</v>
       </c>
       <c r="D12" t="n">
-        <v>1.116389108907252</v>
+        <v>1.097199034281422</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -824,17 +824,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TMNT_CLT_NUM</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5390312542409413</v>
+        <v>0.5420107215366481</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003943831330575243</v>
+        <v>0.00380586140159499</v>
       </c>
       <c r="D13" t="n">
-        <v>1.119025623093961</v>
+        <v>1.172670472529229</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -843,17 +843,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPCT_YN</t>
+          <t>LBST_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5389194858233991</v>
+        <v>0.5408115195586706</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003880767572635963</v>
+        <v>0.003580103909639817</v>
       </c>
       <c r="D14" t="n">
-        <v>1.101131865702375</v>
+        <v>1.103109572424686</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -862,17 +862,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5381939686089772</v>
+        <v>0.5396393502764638</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003859341126852311</v>
+        <v>0.004214741324079186</v>
       </c>
       <c r="D15" t="n">
-        <v>1.09505231010428</v>
+        <v>1.29865546286711</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -881,17 +881,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LBST_EXE_SUM_AMT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5372152019313683</v>
+        <v>0.5392026379213561</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003829171910607605</v>
+        <v>0.003522438628760229</v>
       </c>
       <c r="D16" t="n">
-        <v>1.086492074339439</v>
+        <v>1.085341617934999</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -900,17 +900,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>AID_BIZ_EXE_TY_CD</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5336586215984073</v>
+        <v>0.5368930610192355</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003883324399296815</v>
+        <v>0.003517556737091153</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10185734159307</v>
+        <v>1.083837398625275</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -919,17 +919,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AID_BIZ_EXE_TY_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5322008229983045</v>
+        <v>0.5362428540281104</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003778841558535783</v>
+        <v>0.003583608447263103</v>
       </c>
       <c r="D18" t="n">
-        <v>1.072211302960838</v>
+        <v>1.104189398345035</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -938,17 +938,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5313246326721544</v>
+        <v>0.5339217389068401</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003910825830512247</v>
+        <v>0.003611332294837258</v>
       </c>
       <c r="D19" t="n">
-        <v>1.109660618057568</v>
+        <v>1.112731731868133</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -957,17 +957,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LBST_EXE_AVG_AMT</t>
+          <t>LODI_CNT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5310036184427235</v>
+        <v>0.5325959425035319</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003826554750658763</v>
+        <v>0.003522441688832761</v>
       </c>
       <c r="D20" t="n">
-        <v>1.085749479436918</v>
+        <v>1.085342560811348</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -976,17 +976,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LODI_CNT</t>
+          <t>TMNT_CLT_NUM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5309727899321528</v>
+        <v>0.5323037213752917</v>
       </c>
       <c r="C21" t="n">
-        <v>0.003819713865870985</v>
+        <v>0.003614848678399931</v>
       </c>
       <c r="D21" t="n">
-        <v>1.083808441719912</v>
+        <v>1.11381520778565</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_AMT</t>
+          <t>AID_BIZ_DPI_DV_CD</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5292929269410506</v>
+        <v>0.5292940530079201</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003900136415858524</v>
+        <v>0.003447784372087854</v>
       </c>
       <c r="D22" t="n">
-        <v>1.106627595625635</v>
+        <v>1.062338982470759</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -1014,17 +1014,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AID_BIZ_DPI_DV_CD</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5283919230342171</v>
+        <v>0.5283204087837603</v>
       </c>
       <c r="C23" t="n">
-        <v>0.003736817562832833</v>
+        <v>0.003597886647225243</v>
       </c>
       <c r="D23" t="n">
-        <v>1.060287383291197</v>
+        <v>1.108588829046702</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -1033,17 +1033,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5279497097734592</v>
+        <v>0.5276086138227275</v>
       </c>
       <c r="C24" t="n">
-        <v>0.004374174167775467</v>
+        <v>0.003595269992398425</v>
       </c>
       <c r="D24" t="n">
-        <v>1.241131418493624</v>
+        <v>1.107782579546674</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1052,17 +1052,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5267137932937535</v>
+        <v>0.5273963230484093</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003901703621509663</v>
+        <v>0.003508039652314369</v>
       </c>
       <c r="D25" t="n">
-        <v>1.107072275717983</v>
+        <v>1.080904973314775</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1071,17 +1071,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
+          <t>CONT_BIZ_YN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5260076366611558</v>
+        <v>0.5263770990173797</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003785290955261598</v>
+        <v>0.003431180505697649</v>
       </c>
       <c r="D26" t="n">
-        <v>1.074041259565152</v>
+        <v>1.057222962261128</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5242299670126831</v>
+        <v>0.5261580526645433</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003745409623058473</v>
+        <v>0.003480421910136889</v>
       </c>
       <c r="D27" t="n">
-        <v>1.06272530082411</v>
+        <v>1.07239533322229</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1109,17 +1109,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CARD_FR_USE_CNT</t>
+          <t>PBAC_TY_DV_CD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5221473590659509</v>
+        <v>0.5258992581122339</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003732260260705289</v>
+        <v>0.003423424015914176</v>
       </c>
       <c r="D28" t="n">
-        <v>1.058994291009749</v>
+        <v>1.0548330153924</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -1128,17 +1128,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PBAC_TY_DV_CD</t>
+          <t>NTS_BT_CD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5219300908276755</v>
+        <v>0.5254248477353729</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003693724027249403</v>
+        <v>0.003454149577878362</v>
       </c>
       <c r="D29" t="n">
-        <v>1.048059991583618</v>
+        <v>1.064300243823832</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1147,17 +1147,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CARD_RTRCN_CNT</t>
+          <t>PRIV_AID_BIZ_CGP_YN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5218809327821228</v>
+        <v>0.5253439024666549</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003797378246378105</v>
+        <v>0.003421221114454581</v>
       </c>
       <c r="D30" t="n">
-        <v>1.077470916500099</v>
+        <v>1.054154252499333</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1166,17 +1166,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_CNT</t>
+          <t>TMNT_INDV_BZR_CLT_NUM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5214865714342583</v>
+        <v>0.5253388154346381</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00371819400007944</v>
+        <v>0.003532912943437238</v>
       </c>
       <c r="D31" t="n">
-        <v>1.055003119800318</v>
+        <v>1.088568987049534</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1185,17 +1185,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5206475769103995</v>
+        <v>0.5233817578085069</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0039350253033335</v>
+        <v>0.003482533176817451</v>
       </c>
       <c r="D32" t="n">
-        <v>1.116526994401405</v>
+        <v>1.073045861403608</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -1204,17 +1204,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NTS_BT_CD</t>
+          <t>FYR</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5204976954578555</v>
+        <v>0.5211636087832021</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003707395255833129</v>
+        <v>0.003493648674309353</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0519390761088</v>
+        <v>1.076470793191918</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1223,17 +1223,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TMNT_EXE_CNT</t>
+          <t>ETC_EXE_CNT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5198848773329932</v>
+        <v>0.521159305777018</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003706484671872581</v>
+        <v>0.003481338638157068</v>
       </c>
       <c r="D34" t="n">
-        <v>1.051680706341327</v>
+        <v>1.072677797497041</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -1242,17 +1242,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AID_BIZ_DV_CD</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5195940788657246</v>
+        <v>0.5208445131762683</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003671895134229387</v>
+        <v>0.003563029752492529</v>
       </c>
       <c r="D35" t="n">
-        <v>1.041866245308568</v>
+        <v>1.097848645181892</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -1261,17 +1261,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETC_EXE_CNT</t>
+          <t>ODN_CAPT_DV_CD</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5186388528144287</v>
+        <v>0.5202024678608377</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003780907848913768</v>
+        <v>0.003381870465804889</v>
       </c>
       <c r="D36" t="n">
-        <v>1.072797593723273</v>
+        <v>1.042029443191504</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -1280,17 +1280,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_DLNG_AMT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5186004642736314</v>
+        <v>0.5200161728582947</v>
       </c>
       <c r="C37" t="n">
-        <v>0.003786564803615549</v>
+        <v>0.003324221225866052</v>
       </c>
       <c r="D37" t="n">
-        <v>1.074402702240693</v>
+        <v>1.024266431272127</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -1299,17 +1299,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ODN_CAPT_DV_CD</t>
+          <t>ACNT_DV_CD</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5176765123299326</v>
+        <v>0.5196067552330154</v>
       </c>
       <c r="C38" t="n">
-        <v>0.003653230649128051</v>
+        <v>0.003564583272714486</v>
       </c>
       <c r="D38" t="n">
-        <v>1.03657037048037</v>
+        <v>1.098327319284949</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -1318,17 +1318,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ACNT_DV_CD</t>
+          <t>AID_BIZ_DV_CD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5174958044667096</v>
+        <v>0.5192295698731296</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003812607328839443</v>
+        <v>0.003379612163459114</v>
       </c>
       <c r="D39" t="n">
-        <v>1.08179202763848</v>
+        <v>1.041333610054274</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -1337,17 +1337,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LBST_EXE_RT_DV_CD</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5171657409638333</v>
+        <v>0.5170874609718751</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003752695715876162</v>
+        <v>0.003378631456029198</v>
       </c>
       <c r="D40" t="n">
-        <v>1.064792662197307</v>
+        <v>1.041031432301619</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -1356,17 +1356,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EXE_PLAN_CHG_TMS</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5170924249237971</v>
+        <v>0.5169179855658851</v>
       </c>
       <c r="C41" t="n">
-        <v>0.003655367032457397</v>
+        <v>0.003367512876676662</v>
       </c>
       <c r="D41" t="n">
-        <v>1.037176549468745</v>
+        <v>1.037605550923561</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -1375,17 +1375,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>TMNT_EXE_AMT</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5169506041156696</v>
+        <v>0.516696102517889</v>
       </c>
       <c r="C42" t="n">
-        <v>0.003790251224110331</v>
+        <v>0.003565527458554109</v>
       </c>
       <c r="D42" t="n">
-        <v>1.075448689922565</v>
+        <v>1.098618243924044</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -1394,17 +1394,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CONT_BIZ_YN</t>
+          <t>INDV_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5157797002840989</v>
+        <v>0.5163873624470696</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003640746574098707</v>
+        <v>0.003440438999690085</v>
       </c>
       <c r="D43" t="n">
-        <v>1.033028129784081</v>
+        <v>1.060075710004508</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -1413,17 +1413,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TMNT_EXE_AMT</t>
+          <t>CARD_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5156820666578075</v>
+        <v>0.5159450497887964</v>
       </c>
       <c r="C44" t="n">
-        <v>0.003796962309823611</v>
+        <v>0.003370333263437088</v>
       </c>
       <c r="D44" t="n">
-        <v>1.077352898354025</v>
+        <v>1.03847457475971</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -1432,17 +1432,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_AMT</t>
+          <t>EXE_PLAN_CHG_TMS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5148413981002571</v>
+        <v>0.5158741398846266</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003776923801335477</v>
+        <v>0.003355703063720464</v>
       </c>
       <c r="D45" t="n">
-        <v>1.071667157112262</v>
+        <v>1.033966685111469</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -1451,17 +1451,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_CNT</t>
+          <t>TMNT_CORP_CLT_NUM</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5145520905561209</v>
+        <v>0.5158158233953907</v>
       </c>
       <c r="C46" t="n">
-        <v>0.003662513637577656</v>
+        <v>0.003571445535361535</v>
       </c>
       <c r="D46" t="n">
-        <v>1.039204332499349</v>
+        <v>1.10044173490123</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -1470,17 +1470,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>LBST_EXE_RT_DV_CD</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5125963236298311</v>
+        <v>0.5149116792408132</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003740671982364737</v>
+        <v>0.003413090430529153</v>
       </c>
       <c r="D47" t="n">
-        <v>1.061381039144306</v>
+        <v>1.051649008100044</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -1489,17 +1489,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
+          <t>TMNT_EXE_CNT</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.512592554744144</v>
+        <v>0.514261549904789</v>
       </c>
       <c r="C48" t="n">
-        <v>0.003670689430659172</v>
+        <v>0.003355144383326447</v>
       </c>
       <c r="D48" t="n">
-        <v>1.041524138084441</v>
+        <v>1.033794543266952</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -1508,17 +1508,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>INDV_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5125509575687746</v>
+        <v>0.5115497224864157</v>
       </c>
       <c r="C49" t="n">
-        <v>0.003646198457463608</v>
+        <v>0.003381430773260546</v>
       </c>
       <c r="D49" t="n">
-        <v>1.03457505120847</v>
+        <v>1.041893964147647</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -1527,17 +1527,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5125177335017115</v>
+        <v>0.5110866082275073</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00365839244123692</v>
+        <v>0.01582347427300902</v>
       </c>
       <c r="D50" t="n">
-        <v>1.03803498119689</v>
+        <v>4.875564056275702</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -1546,17 +1546,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TMNT_INDV_DLNG_AMT</t>
+          <t>TMNT_INDV_BZR_DLNG_AMT</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5104679057049294</v>
+        <v>0.5103821527116879</v>
       </c>
       <c r="C51" t="n">
-        <v>0.00357260488562436</v>
+        <v>0.003446195810906694</v>
       </c>
       <c r="D51" t="n">
-        <v>1.013693556621045</v>
+        <v>1.061849511469484</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1565,17 +1565,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>INDV_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.510141789998516</v>
+        <v>0.5100964982150622</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003672181660963915</v>
+        <v>0.003460614357021484</v>
       </c>
       <c r="D52" t="n">
-        <v>1.041947544616465</v>
+        <v>1.066292185939586</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -1584,17 +1584,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5099980797078048</v>
+        <v>0.5097223380819718</v>
       </c>
       <c r="C53" t="n">
-        <v>0.003593159691845653</v>
+        <v>0.003340206920701427</v>
       </c>
       <c r="D53" t="n">
-        <v>1.019525792564057</v>
+        <v>1.02919197908857</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -1603,17 +1603,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TMNT_INDV_CLT_NUM</t>
+          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5098880088427415</v>
+        <v>0.5097172996363016</v>
       </c>
       <c r="C54" t="n">
-        <v>0.003596594381129774</v>
+        <v>0.003368872853955759</v>
       </c>
       <c r="D54" t="n">
-        <v>1.020500353845748</v>
+        <v>1.038024590144968</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5092344838966056</v>
+        <v>0.5096960200622909</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0038022834007718</v>
+        <v>0.003437294063891046</v>
       </c>
       <c r="D55" t="n">
-        <v>1.078862708641213</v>
+        <v>1.059106685397362</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1641,17 +1641,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TMNT_CORP_CLT_NUM</t>
+          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5083949245018701</v>
+        <v>0.5088206448386565</v>
       </c>
       <c r="C56" t="n">
-        <v>0.003751236325290547</v>
+        <v>0.003483479100347937</v>
       </c>
       <c r="D56" t="n">
-        <v>1.064378573631514</v>
+        <v>1.073337321463874</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -1660,17 +1660,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
+          <t>INDV_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5080490290752421</v>
+        <v>0.5087932774369425</v>
       </c>
       <c r="C57" t="n">
-        <v>0.003669735573434534</v>
+        <v>0.003324219592079169</v>
       </c>
       <c r="D57" t="n">
-        <v>1.041253489928962</v>
+        <v>1.024265927866083</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -1679,17 +1679,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
+          <t>INVC_EXE_CNT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5076015749046904</v>
+        <v>0.5073025943381575</v>
       </c>
       <c r="C58" t="n">
-        <v>0.003620305525574961</v>
+        <v>0.003300668094053085</v>
       </c>
       <c r="D58" t="n">
-        <v>1.027228171534436</v>
+        <v>1.017009187957623</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -1698,17 +1698,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
+          <t>TMNT_INDV_CLT_NUM</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5075116327618483</v>
+        <v>0.5071974293985568</v>
       </c>
       <c r="C59" t="n">
-        <v>0.003548607011692489</v>
+        <v>0.003380306708912013</v>
       </c>
       <c r="D59" t="n">
-        <v>1.006884382095413</v>
+        <v>1.041547614942656</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -1717,17 +1717,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
+          <t>PRIV_AID_BZR_YN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5072905998376692</v>
+        <v>0.5065540813876619</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003525029450569473</v>
+        <v>0.003288455027911747</v>
       </c>
       <c r="D60" t="n">
-        <v>1.000194467437509</v>
+        <v>1.013246070878007</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -1736,17 +1736,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EVENT_FSTV_YN</t>
+          <t>TMNT_INDV_DLNG_AMT</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.507066787496789</v>
+        <v>0.5062834035285614</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003606507808457418</v>
+        <v>0.003287188609086437</v>
       </c>
       <c r="D61" t="n">
-        <v>1.023313197058973</v>
+        <v>1.012855859095289</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -1759,13 +1759,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5048871813510046</v>
+        <v>0.5058392429280455</v>
       </c>
       <c r="C62" t="n">
-        <v>0.003642287846943766</v>
+        <v>0.003350829880802737</v>
       </c>
       <c r="D62" t="n">
-        <v>1.033465451682822</v>
+        <v>1.032465149161563</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -1774,17 +1774,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_AMT</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5048036442979345</v>
+        <v>0.505462729056386</v>
       </c>
       <c r="C63" t="n">
-        <v>0.003583421882772224</v>
+        <v>0.003385789540039949</v>
       </c>
       <c r="D63" t="n">
-        <v>1.016762779404371</v>
+        <v>1.043236997053865</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -1793,17 +1793,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>INVC_EXE_CNT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5047242037136622</v>
+        <v>0.5050176486374277</v>
       </c>
       <c r="C64" t="n">
-        <v>0.003560905908159108</v>
+        <v>0.003311418286362922</v>
       </c>
       <c r="D64" t="n">
-        <v>1.010374080089145</v>
+        <v>1.020321561101446</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -1812,17 +1812,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TMNT_CORP_DLNG_AMT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5046361187150711</v>
+        <v>0.5049399835700077</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00358606267864706</v>
+        <v>0.003255388777023212</v>
       </c>
       <c r="D65" t="n">
-        <v>1.017512080782042</v>
+        <v>1.003057624173674</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -1831,17 +1831,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NTN_DRCT_BIZ_YN</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5038484917428494</v>
+        <v>0.5047469226072485</v>
       </c>
       <c r="C66" t="n">
-        <v>0.003572372405338638</v>
+        <v>0.003233363701681251</v>
       </c>
       <c r="D66" t="n">
-        <v>1.013627592492567</v>
+        <v>0.9962712090146975</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -1850,17 +1850,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_CNT</t>
+          <t>ETI_EXE_CNT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5035494377612115</v>
+        <v>0.5043638520704046</v>
       </c>
       <c r="C67" t="n">
-        <v>0.003575217340710721</v>
+        <v>0.003293738443247539</v>
       </c>
       <c r="D67" t="n">
-        <v>1.014434816562401</v>
+        <v>1.014874008552195</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -1869,17 +1869,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CB_YN</t>
+          <t>CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5034991134357887</v>
+        <v>0.5042593457457246</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003549093994098011</v>
+        <v>0.003309959930171629</v>
       </c>
       <c r="D68" t="n">
-        <v>1.007022558843884</v>
+        <v>1.019872209150994</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -1888,17 +1888,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LSA_MNG_CMMT_DLBR_YN</t>
+          <t>EVENT_FSTV_YN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.503487271726313</v>
+        <v>0.5042373282406204</v>
       </c>
       <c r="C69" t="n">
-        <v>0.003581367076482868</v>
+        <v>0.003283236679381769</v>
       </c>
       <c r="D69" t="n">
-        <v>1.01617974714575</v>
+        <v>1.011638181732621</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
@@ -1907,17 +1907,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5034130716318562</v>
+        <v>0.5040854768051439</v>
       </c>
       <c r="C70" t="n">
-        <v>0.003375999697471452</v>
+        <v>0.003301821808960061</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9579086549010664</v>
+        <v>1.017364673158571</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -1926,17 +1926,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>NTN_DRCT_BIZ_YN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5032851542069103</v>
+        <v>0.5040737591902528</v>
       </c>
       <c r="C71" t="n">
-        <v>0.003798928324279264</v>
+        <v>0.003292080288896853</v>
       </c>
       <c r="D71" t="n">
-        <v>1.077910736751979</v>
+        <v>1.014363094348874</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -1945,17 +1945,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PRIV_AID_BIZ_CGP_YN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5030307754219479</v>
+        <v>0.5035697165404435</v>
       </c>
       <c r="C72" t="n">
-        <v>0.003545772831115786</v>
+        <v>0.003460520950933457</v>
       </c>
       <c r="D72" t="n">
-        <v>1.006080209599187</v>
+        <v>1.066263405448175</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -1964,17 +1964,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>CB_YN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5029414254485752</v>
+        <v>0.503129107726445</v>
       </c>
       <c r="C73" t="n">
-        <v>0.01683112620466605</v>
+        <v>0.003265837539623402</v>
       </c>
       <c r="D73" t="n">
-        <v>4.775676216812837</v>
+        <v>1.006277120125517</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -1983,17 +1983,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SBAT_EXE_SUM_AMT</t>
+          <t>CORP_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.502661775306531</v>
+        <v>0.5031060898409222</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003611209689715584</v>
+        <v>0.003332726814101617</v>
       </c>
       <c r="D74" t="n">
-        <v>1.02464731233004</v>
+        <v>1.026887192020577</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
@@ -2002,17 +2002,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TMNT_DLNG_AMT</t>
+          <t>VNCL_GOEM_VRSC_YN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.502661775306531</v>
+        <v>0.5027770286344506</v>
       </c>
       <c r="C75" t="n">
-        <v>0.003611209689715584</v>
+        <v>0.003263533460838379</v>
       </c>
       <c r="D75" t="n">
-        <v>1.02464731233004</v>
+        <v>1.005567182250101</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -2021,17 +2021,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VNCL_GOEM_VRSC_YN</t>
+          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5023369342344012</v>
+        <v>0.5019247576720666</v>
       </c>
       <c r="C76" t="n">
-        <v>0.003540835988718888</v>
+        <v>0.003258027815122984</v>
       </c>
       <c r="D76" t="n">
-        <v>1.00467942628057</v>
+        <v>1.003870770457505</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -2040,17 +2040,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
+          <t>LSA_MNG_CMMT_DLBR_YN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5013349402343262</v>
+        <v>0.5018066048130083</v>
       </c>
       <c r="C77" t="n">
-        <v>0.003535771000806246</v>
+        <v>0.003264822394257026</v>
       </c>
       <c r="D77" t="n">
-        <v>1.003242282858394</v>
+        <v>1.005964331279351</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -2059,17 +2059,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PBCN_DGR</t>
+          <t>TMNT_DLNG_AMT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5010000154820817</v>
+        <v>0.501789880728077</v>
       </c>
       <c r="C78" t="n">
-        <v>0.003531382300781229</v>
+        <v>0.003326103108533695</v>
       </c>
       <c r="D78" t="n">
-        <v>1.001997029862407</v>
+        <v>1.024846281141643</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
@@ -2078,17 +2078,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AST_LAT_RT</t>
+          <t>SBAT_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5009737512961876</v>
+        <v>0.5017894189501502</v>
       </c>
       <c r="C79" t="n">
-        <v>0.00353128722509514</v>
+        <v>0.003326097916930697</v>
       </c>
       <c r="D79" t="n">
-        <v>1.00197005301681</v>
+        <v>1.024844681493391</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -2097,17 +2097,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>PBCN_DGR</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5007632195106</v>
+        <v>0.5012132085496424</v>
       </c>
       <c r="C80" t="n">
-        <v>0.003656098728277908</v>
+        <v>0.003253334018405725</v>
       </c>
       <c r="D80" t="n">
-        <v>1.037384161382854</v>
+        <v>1.002424507382324</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CUMU_EXE_AMT</t>
+          <t>AST_LAT_RT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5007191633620083</v>
+        <v>0.5008661006299149</v>
       </c>
       <c r="C81" t="n">
-        <v>0.003568195439636439</v>
+        <v>0.003250909419827864</v>
       </c>
       <c r="D81" t="n">
-        <v>1.012442417150176</v>
+        <v>1.001677434680516</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RERE_DSCRD_CNT</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5004715680673085</v>
+        <v>0.5008418452459913</v>
       </c>
       <c r="C82" t="n">
-        <v>0.003609490165610487</v>
+        <v>0.003115840495814372</v>
       </c>
       <c r="D82" t="n">
-        <v>1.024159413286738</v>
+        <v>0.9600596976603148</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
@@ -2154,17 +2154,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PRIV_AID_BZR_YN</t>
+          <t>TMNT_CORP_DLNG_AMT</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5004591455277789</v>
+        <v>0.5003170213436747</v>
       </c>
       <c r="C83" t="n">
-        <v>0.003527692321817611</v>
+        <v>0.003231417296628579</v>
       </c>
       <c r="D83" t="n">
-        <v>1.000950032497953</v>
+        <v>0.9956714783645235</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -2173,17 +2173,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ETI_EXE_CNT</t>
+          <t>RERE_DSCRD_CNT</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5001463964722196</v>
+        <v>0.500194525612712</v>
       </c>
       <c r="C84" t="n">
-        <v>0.00352495556359978</v>
+        <v>0.003323987596027563</v>
       </c>
       <c r="D84" t="n">
-        <v>1.000173502693997</v>
+        <v>1.024194444727115</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9998677512211543</v>
+        <v>0.9999082090604214</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1975</v>
+        <v>1924</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9966267973811307</v>
+        <v>0.9968577994433535</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9964756559195928</v>
+        <v>0.9967545346363276</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">

--- a/outputs/reports/comparison/leakage_audit.xlsx
+++ b/outputs/reports/comparison/leakage_audit.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="요약(summary)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="제외정책(checklist)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="단변량(univariate)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="의심피처(suspects)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="라벨정의검증(label_def)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="피처목록(feature_list)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약(summary)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외정책(checklist)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량(univariate)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="의심피처(suspects)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라벨정의검증(label_def)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="피처목록(feature_list)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003245465363672425</v>
+        <v>0.003379762763862648</v>
       </c>
     </row>
     <row r="4">
@@ -615,17 +615,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5953456177723242</v>
+        <v>0.6053013709396988</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004388227477903696</v>
+        <v>0.004713153125455861</v>
       </c>
       <c r="D2" t="n">
-        <v>1.352110402108304</v>
+        <v>1.39452188060363</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -634,17 +634,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5865129899625758</v>
+        <v>0.5991175197519107</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00451154947971646</v>
+        <v>0.004417100539164517</v>
       </c>
       <c r="D3" t="n">
-        <v>1.390108651355746</v>
+        <v>1.306926209849215</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -653,17 +653,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5665283492279621</v>
+        <v>0.5980091127479635</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003816934440223919</v>
+        <v>0.005085482275452633</v>
       </c>
       <c r="D4" t="n">
-        <v>1.176082321798328</v>
+        <v>1.504686166090711</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -672,17 +672,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5639898417659797</v>
+        <v>0.591860654484926</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004020446872672561</v>
+        <v>0.004655132952401041</v>
       </c>
       <c r="D5" t="n">
-        <v>1.238789024734253</v>
+        <v>1.377354944014119</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -691,17 +691,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>CUMU_PYHWY_EXE_CNT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5635780338585543</v>
+        <v>0.5726737968486489</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003781455584011756</v>
+        <v>0.004425600632325504</v>
       </c>
       <c r="D6" t="n">
-        <v>1.165150497780333</v>
+        <v>1.309441206834173</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -710,17 +710,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5598697291247227</v>
+        <v>0.5706553225969345</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003659745890894433</v>
+        <v>0.004098844419317701</v>
       </c>
       <c r="D7" t="n">
-        <v>1.127649036671039</v>
+        <v>1.212760985221706</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -729,17 +729,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.55683852371723</v>
+        <v>0.568511896543703</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005400036456637725</v>
+        <v>0.003969343101247478</v>
       </c>
       <c r="D8" t="n">
-        <v>1.663871233100231</v>
+        <v>1.174444296412986</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -748,17 +748,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_CNT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5476144328059797</v>
+        <v>0.5579909450956826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003792557774419537</v>
+        <v>0.003959733708587523</v>
       </c>
       <c r="D9" t="n">
-        <v>1.168571329360313</v>
+        <v>1.171601081272947</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -767,17 +767,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OPCT_YN</t>
+          <t>AID_BIZ_EXE_TY_CD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5464846449371249</v>
+        <v>0.5429081753513888</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003663743761293497</v>
+        <v>0.003712512236963653</v>
       </c>
       <c r="D10" t="n">
-        <v>1.128880869382555</v>
+        <v>1.098453499949421</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -786,17 +786,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LBST_EXE_CNT</t>
+          <t>TMNT_CLT_NUM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5444679008528904</v>
+        <v>0.5392673636857247</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00369384421156972</v>
+        <v>0.003762360171311574</v>
       </c>
       <c r="D11" t="n">
-        <v>1.138155487011554</v>
+        <v>1.11320244472179</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,17 +805,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_AMT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5435407363211828</v>
+        <v>0.5392340614246112</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003560921462815187</v>
+        <v>0.003703497033318717</v>
       </c>
       <c r="D12" t="n">
-        <v>1.097199034281422</v>
+        <v>1.095786092715597</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -824,17 +824,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>INDV_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5420107215366481</v>
+        <v>0.5386703962544304</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00380586140159499</v>
+        <v>0.003841486014310072</v>
       </c>
       <c r="D13" t="n">
-        <v>1.172670472529229</v>
+        <v>1.136614100665377</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -843,17 +843,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LBST_EXE_SUM_AMT</t>
+          <t>TMNT_INDV_BZR_CLT_NUM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5408115195586706</v>
+        <v>0.5386570597334498</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003580103909639817</v>
+        <v>0.003786533084775968</v>
       </c>
       <c r="D14" t="n">
-        <v>1.103109572424686</v>
+        <v>1.120354696271176</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -862,17 +862,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5396393502764638</v>
+        <v>0.5311851801549257</v>
       </c>
       <c r="C15" t="n">
-        <v>0.004214741324079186</v>
+        <v>0.005920462364369126</v>
       </c>
       <c r="D15" t="n">
-        <v>1.29865546286711</v>
+        <v>1.751739035553719</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -881,17 +881,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5392026379213561</v>
+        <v>0.5311725776110954</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003522438628760229</v>
+        <v>0.003813109567881095</v>
       </c>
       <c r="D16" t="n">
-        <v>1.085341617934999</v>
+        <v>1.128218113014295</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -900,17 +900,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AID_BIZ_EXE_TY_CD</t>
+          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5368930610192355</v>
+        <v>0.5304939805987352</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003517556737091153</v>
+        <v>0.003661609091067947</v>
       </c>
       <c r="D17" t="n">
-        <v>1.083837398625275</v>
+        <v>1.083392340497646</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -919,17 +919,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>AID_BIZ_DV_CD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5362428540281104</v>
+        <v>0.5301924018810366</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003583608447263103</v>
+        <v>0.003601817248134569</v>
       </c>
       <c r="D18" t="n">
-        <v>1.104189398345035</v>
+        <v>1.06570120442955</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -938,17 +938,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LBST_EXE_AVG_AMT</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5339217389068401</v>
+        <v>0.5276197729290206</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003611332294837258</v>
+        <v>0.003942193601391267</v>
       </c>
       <c r="D19" t="n">
-        <v>1.112731731868133</v>
+        <v>1.166411336186754</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -957,17 +957,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LODI_CNT</t>
+          <t>TMNT_INDV_BZR_DLNG_AMT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5325959425035319</v>
+        <v>0.5258162251458354</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003522441688832761</v>
+        <v>0.003691196013812182</v>
       </c>
       <c r="D20" t="n">
-        <v>1.085342560811348</v>
+        <v>1.092146482374285</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -976,17 +976,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TMNT_CLT_NUM</t>
+          <t>TMNT_EXE_AMT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5323037213752917</v>
+        <v>0.5255621050783239</v>
       </c>
       <c r="C21" t="n">
-        <v>0.003614848678399931</v>
+        <v>0.003726397731192884</v>
       </c>
       <c r="D21" t="n">
-        <v>1.11381520778565</v>
+        <v>1.102561922699591</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AID_BIZ_DPI_DV_CD</t>
+          <t>LBST_EXE_CNT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5292940530079201</v>
+        <v>0.5249994745035937</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003447784372087854</v>
+        <v>0.003674031827674029</v>
       </c>
       <c r="D22" t="n">
-        <v>1.062338982470759</v>
+        <v>1.087067964342878</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -1014,17 +1014,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5283204087837603</v>
+        <v>0.5248864322621625</v>
       </c>
       <c r="C23" t="n">
-        <v>0.003597886647225243</v>
+        <v>0.00370626485744985</v>
       </c>
       <c r="D23" t="n">
-        <v>1.108588829046702</v>
+        <v>1.096605033074585</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -1033,17 +1033,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>TMNT_EXE_CNT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5276086138227275</v>
+        <v>0.5244747491636994</v>
       </c>
       <c r="C24" t="n">
-        <v>0.003595269992398425</v>
+        <v>0.003608641685081744</v>
       </c>
       <c r="D24" t="n">
-        <v>1.107782579546674</v>
+        <v>1.067720410339546</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1052,17 +1052,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
+          <t>PBAC_TY_DV_CD</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5273963230484093</v>
+        <v>0.5233045943799433</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003508039652314369</v>
+        <v>0.003610546976529176</v>
       </c>
       <c r="D25" t="n">
-        <v>1.080904973314775</v>
+        <v>1.068284145601619</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1071,17 +1071,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONT_BIZ_YN</t>
+          <t>LBST_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5263770990173797</v>
+        <v>0.5219652637193175</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003431180505697649</v>
+        <v>0.003577588124866324</v>
       </c>
       <c r="D26" t="n">
-        <v>1.057222962261128</v>
+        <v>1.058532321593361</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -1090,17 +1090,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CUMU_EXE_CNT</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5261580526645433</v>
+        <v>0.5210444640077985</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003480421910136889</v>
+        <v>0.004005418475789617</v>
       </c>
       <c r="D27" t="n">
-        <v>1.07239533322229</v>
+        <v>1.185118233331834</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1109,17 +1109,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PBAC_TY_DV_CD</t>
+          <t>EXE_PLAN_CHG_TMS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5258992581122339</v>
+        <v>0.5209092384782492</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003423424015914176</v>
+        <v>0.00354088536532958</v>
       </c>
       <c r="D28" t="n">
-        <v>1.0548330153924</v>
+        <v>1.047672754783175</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -1128,17 +1128,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NTS_BT_CD</t>
+          <t>INDV_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5254248477353729</v>
+        <v>0.5202057682295993</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003454149577878362</v>
+        <v>0.003554389869566619</v>
       </c>
       <c r="D29" t="n">
-        <v>1.064300243823832</v>
+        <v>1.05166845068865</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1147,17 +1147,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PRIV_AID_BIZ_CGP_YN</t>
+          <t>ACNT_DV_CD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5253439024666549</v>
+        <v>0.5198670436310843</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003421221114454581</v>
+        <v>0.003707011892182272</v>
       </c>
       <c r="D30" t="n">
-        <v>1.054154252499333</v>
+        <v>1.096826064781428</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1166,17 +1166,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>CARD_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5253388154346381</v>
+        <v>0.5193578040378144</v>
       </c>
       <c r="C31" t="n">
-        <v>0.003532912943437238</v>
+        <v>0.003686580453424638</v>
       </c>
       <c r="D31" t="n">
-        <v>1.088568987049534</v>
+        <v>1.090780836111507</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1185,17 +1185,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>AID_BIZ_DPI_DV_CD</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5233817578085069</v>
+        <v>0.5193508566317592</v>
       </c>
       <c r="C32" t="n">
-        <v>0.003482533176817451</v>
+        <v>0.003515958794429289</v>
       </c>
       <c r="D32" t="n">
-        <v>1.073045861403608</v>
+        <v>1.040297512009685</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -1204,17 +1204,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>OPCT_YN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5211636087832021</v>
+        <v>0.5191210495573407</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003493648674309353</v>
+        <v>0.003529328021352844</v>
       </c>
       <c r="D33" t="n">
-        <v>1.076470793191918</v>
+        <v>1.044253182232016</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1223,17 +1223,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETC_EXE_CNT</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.521159305777018</v>
+        <v>0.5190472848537676</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003481338638157068</v>
+        <v>0.003574500392280498</v>
       </c>
       <c r="D34" t="n">
-        <v>1.072677797497041</v>
+        <v>1.057618727118968</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -1242,17 +1242,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>INDV_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5208445131762683</v>
+        <v>0.5172821244659399</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003563029752492529</v>
+        <v>0.00364255759657843</v>
       </c>
       <c r="D35" t="n">
-        <v>1.097848645181892</v>
+        <v>1.077755408020248</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -1261,17 +1261,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ODN_CAPT_DV_CD</t>
+          <t>FYR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5202024678608377</v>
+        <v>0.5162397636930894</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003381870465804889</v>
+        <v>0.003685178258303364</v>
       </c>
       <c r="D36" t="n">
-        <v>1.042029443191504</v>
+        <v>1.090365956364246</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -1280,17 +1280,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>INDV_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5200161728582947</v>
+        <v>0.5161191610966001</v>
       </c>
       <c r="C37" t="n">
-        <v>0.003324221225866052</v>
+        <v>0.003524130313308992</v>
       </c>
       <c r="D37" t="n">
-        <v>1.024266431272127</v>
+        <v>1.042715290845251</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -1299,17 +1299,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ACNT_DV_CD</t>
+          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5196067552330154</v>
+        <v>0.5160412814360266</v>
       </c>
       <c r="C38" t="n">
-        <v>0.003564583272714486</v>
+        <v>0.003555484379227469</v>
       </c>
       <c r="D38" t="n">
-        <v>1.098327319284949</v>
+        <v>1.051992292844836</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -1318,17 +1318,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AID_BIZ_DV_CD</t>
+          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5192295698731296</v>
+        <v>0.5159831196030913</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003379612163459114</v>
+        <v>0.003632429231696977</v>
       </c>
       <c r="D39" t="n">
-        <v>1.041333610054274</v>
+        <v>1.074758640025243</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -1337,17 +1337,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CARD_FR_USE_CNT</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5170874609718751</v>
+        <v>0.5148346932758682</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003378631456029198</v>
+        <v>0.003832274560480501</v>
       </c>
       <c r="D40" t="n">
-        <v>1.041031432301619</v>
+        <v>1.133888627171183</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -1356,17 +1356,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>ETC_EXE_CNT</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5169179855658851</v>
+        <v>0.5130669971531525</v>
       </c>
       <c r="C41" t="n">
-        <v>0.003367512876676662</v>
+        <v>0.003562915883614338</v>
       </c>
       <c r="D41" t="n">
-        <v>1.037605550923561</v>
+        <v>1.054191117113311</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -1375,17 +1375,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TMNT_EXE_AMT</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.516696102517889</v>
+        <v>0.5123974167377492</v>
       </c>
       <c r="C42" t="n">
-        <v>0.003565527458554109</v>
+        <v>0.003591840932793936</v>
       </c>
       <c r="D42" t="n">
-        <v>1.098618243924044</v>
+        <v>1.062749424663437</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -1394,17 +1394,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_AMT</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5163873624470696</v>
+        <v>0.5121086201540349</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003440438999690085</v>
+        <v>0.003504634640979259</v>
       </c>
       <c r="D43" t="n">
-        <v>1.060075710004508</v>
+        <v>1.03694693558133</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -1413,17 +1413,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CARD_RTRCN_CNT</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5159450497887964</v>
+        <v>0.5112794934077218</v>
       </c>
       <c r="C44" t="n">
-        <v>0.003370333263437088</v>
+        <v>0.003477768306317458</v>
       </c>
       <c r="D44" t="n">
-        <v>1.03847457475971</v>
+        <v>1.028997757920382</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -1432,17 +1432,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EXE_PLAN_CHG_TMS</t>
+          <t>LODI_CNT</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5158741398846266</v>
+        <v>0.5112744687875515</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003355703063720464</v>
+        <v>0.003472628611154502</v>
       </c>
       <c r="D45" t="n">
-        <v>1.033966685111469</v>
+        <v>1.027477031312612</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -1451,17 +1451,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TMNT_CORP_CLT_NUM</t>
+          <t>ODN_CAPT_DV_CD</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5158158233953907</v>
+        <v>0.5112051235634134</v>
       </c>
       <c r="C46" t="n">
-        <v>0.003571445535361535</v>
+        <v>0.003457070541255674</v>
       </c>
       <c r="D46" t="n">
-        <v>1.10044173490123</v>
+        <v>1.022873728955068</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -1470,17 +1470,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LBST_EXE_RT_DV_CD</t>
+          <t>TMNT_INDV_CLT_NUM</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5149116792408132</v>
+        <v>0.5109887681819218</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003413090430529153</v>
+        <v>0.003400932694737213</v>
       </c>
       <c r="D47" t="n">
-        <v>1.051649008100044</v>
+        <v>1.006263732798325</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -1489,17 +1489,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TMNT_EXE_CNT</t>
+          <t>TMNT_CORP_DLNG_AMT</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.514261549904789</v>
+        <v>0.5108315487147428</v>
       </c>
       <c r="C48" t="n">
-        <v>0.003355144383326447</v>
+        <v>0.003487936561209469</v>
       </c>
       <c r="D48" t="n">
-        <v>1.033794543266952</v>
+        <v>1.032006328522062</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -1508,17 +1508,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_CNT</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5115497224864157</v>
+        <v>0.510711457559778</v>
       </c>
       <c r="C49" t="n">
-        <v>0.003381430773260546</v>
+        <v>0.003470270349330065</v>
       </c>
       <c r="D49" t="n">
-        <v>1.041893964147647</v>
+        <v>1.026779271739173</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -1527,17 +1527,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5110866082275073</v>
+        <v>0.5106342786912175</v>
       </c>
       <c r="C50" t="n">
-        <v>0.01582347427300902</v>
+        <v>0.003540885449090136</v>
       </c>
       <c r="D50" t="n">
-        <v>4.875564056275702</v>
+        <v>1.047672779566145</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -1546,17 +1546,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_DLNG_AMT</t>
+          <t>TMNT_DLNG_AMT</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5103821527116879</v>
+        <v>0.5099484434148358</v>
       </c>
       <c r="C51" t="n">
-        <v>0.003446195810906694</v>
+        <v>0.003535529976933765</v>
       </c>
       <c r="D51" t="n">
-        <v>1.061849511469484</v>
+        <v>1.046088209130127</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1565,17 +1565,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_AMT</t>
+          <t>SBAT_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5100964982150622</v>
+        <v>0.5099484434148358</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003460614357021484</v>
+        <v>0.003535529976933765</v>
       </c>
       <c r="D52" t="n">
-        <v>1.066292185939586</v>
+        <v>1.046088209130127</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -1584,17 +1584,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
+          <t>CORP_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5097223380819718</v>
+        <v>0.5095566206448938</v>
       </c>
       <c r="C53" t="n">
-        <v>0.003340206920701427</v>
+        <v>0.003469396132173391</v>
       </c>
       <c r="D53" t="n">
-        <v>1.02919197908857</v>
+        <v>1.026520609454938</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -1603,17 +1603,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5097172996363016</v>
+        <v>0.5092080498209948</v>
       </c>
       <c r="C54" t="n">
-        <v>0.003368872853955759</v>
+        <v>0.003443484870956673</v>
       </c>
       <c r="D54" t="n">
-        <v>1.038024590144968</v>
+        <v>1.018854017736203</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -1622,17 +1622,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5096960200622909</v>
+        <v>0.5089980425610237</v>
       </c>
       <c r="C55" t="n">
-        <v>0.003437294063891046</v>
+        <v>0.003539635487016026</v>
       </c>
       <c r="D55" t="n">
-        <v>1.059106685397362</v>
+        <v>1.047302942343404</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1641,17 +1641,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
+          <t>TMNT_INDV_DLNG_AMT</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5088206448386565</v>
+        <v>0.5088921761174736</v>
       </c>
       <c r="C56" t="n">
-        <v>0.003483479100347937</v>
+        <v>0.003409107204659028</v>
       </c>
       <c r="D56" t="n">
-        <v>1.073337321463874</v>
+        <v>1.008682396619709</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -1660,17 +1660,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_CNT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5087932774369425</v>
+        <v>0.5083820346693013</v>
       </c>
       <c r="C57" t="n">
-        <v>0.003324219592079169</v>
+        <v>0.003759197532156529</v>
       </c>
       <c r="D57" t="n">
-        <v>1.024265927866083</v>
+        <v>1.112266686984927</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -1679,17 +1679,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INVC_EXE_CNT</t>
+          <t>EVENT_FSTV_YN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5073025943381575</v>
+        <v>0.5083207143921409</v>
       </c>
       <c r="C58" t="n">
-        <v>0.003300668094053085</v>
+        <v>0.00347603697691705</v>
       </c>
       <c r="D58" t="n">
-        <v>1.017009187957623</v>
+        <v>1.028485494332263</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -1698,17 +1698,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TMNT_INDV_CLT_NUM</t>
+          <t>LBST_EXE_RT_DV_CD</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5071974293985568</v>
+        <v>0.5081886180258135</v>
       </c>
       <c r="C59" t="n">
-        <v>0.003380306708912013</v>
+        <v>0.003467506790545416</v>
       </c>
       <c r="D59" t="n">
-        <v>1.041547614942656</v>
+        <v>1.025961593405594</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -1717,17 +1717,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PRIV_AID_BZR_YN</t>
+          <t>CONT_BIZ_YN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5065540813876619</v>
+        <v>0.5077011732593509</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003288455027911747</v>
+        <v>0.003432923477272989</v>
       </c>
       <c r="D60" t="n">
-        <v>1.013246070878007</v>
+        <v>1.015729125718157</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -1736,17 +1736,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TMNT_INDV_DLNG_AMT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5062834035285614</v>
+        <v>0.5062201674401771</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003287188609086437</v>
+        <v>0.003750715992288435</v>
       </c>
       <c r="D61" t="n">
-        <v>1.012855859095289</v>
+        <v>1.109757179525179</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -1755,17 +1755,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FLD_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5058392429280455</v>
+        <v>0.5054898718883488</v>
       </c>
       <c r="C62" t="n">
-        <v>0.003350829880802737</v>
+        <v>0.00326429030523436</v>
       </c>
       <c r="D62" t="n">
-        <v>1.032465149161563</v>
+        <v>0.9658341526621479</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -1774,17 +1774,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>NTN_DRCT_BIZ_YN</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.505462729056386</v>
+        <v>0.5048388556290527</v>
       </c>
       <c r="C63" t="n">
-        <v>0.003385789540039949</v>
+        <v>0.003441631452218206</v>
       </c>
       <c r="D63" t="n">
-        <v>1.043236997053865</v>
+        <v>1.018305630506696</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -1793,17 +1793,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
+          <t>AST_LAT_RT</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5050176486374277</v>
+        <v>0.5043124573678353</v>
       </c>
       <c r="C64" t="n">
-        <v>0.003311418286362922</v>
+        <v>0.00340983073402057</v>
       </c>
       <c r="D64" t="n">
-        <v>1.020321561101446</v>
+        <v>1.008896473586672</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -1812,17 +1812,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
+          <t>LSA_MNG_CMMT_DLBR_YN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5049399835700077</v>
+        <v>0.5041542931002821</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003255388777023212</v>
+        <v>0.003448634527748728</v>
       </c>
       <c r="D65" t="n">
-        <v>1.003057624173674</v>
+        <v>1.020377691778392</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -1831,17 +1831,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
+          <t>CB_YN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5047469226072485</v>
+        <v>0.5040480011061503</v>
       </c>
       <c r="C66" t="n">
-        <v>0.003233363701681251</v>
+        <v>0.003407254674007619</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9962712090146975</v>
+        <v>1.008134272156295</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -1850,17 +1850,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ETI_EXE_CNT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5043638520704046</v>
+        <v>0.5036704147600245</v>
       </c>
       <c r="C67" t="n">
-        <v>0.003293738443247539</v>
+        <v>0.00347492282233829</v>
       </c>
       <c r="D67" t="n">
-        <v>1.014874008552195</v>
+        <v>1.028155839662215</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -1869,17 +1869,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CUMU_EXE_AMT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5042593457457246</v>
+        <v>0.503590893411198</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003309959930171629</v>
+        <v>0.003649796631633055</v>
       </c>
       <c r="D68" t="n">
-        <v>1.019872209150994</v>
+        <v>1.079897284702253</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -1888,17 +1888,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EVENT_FSTV_YN</t>
+          <t>CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5042373282406204</v>
+        <v>0.5031595451909028</v>
       </c>
       <c r="C69" t="n">
-        <v>0.003283236679381769</v>
+        <v>0.003546758732446809</v>
       </c>
       <c r="D69" t="n">
-        <v>1.011638181732621</v>
+        <v>1.049410559335622</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
@@ -1907,17 +1907,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_CNT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5040854768051439</v>
+        <v>0.5031053519099514</v>
       </c>
       <c r="C70" t="n">
-        <v>0.003301821808960061</v>
+        <v>0.003368428979121521</v>
       </c>
       <c r="D70" t="n">
-        <v>1.017364673158571</v>
+        <v>0.9966465738772226</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -1926,17 +1926,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NTN_DRCT_BIZ_YN</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5040737591902528</v>
+        <v>0.502994390571823</v>
       </c>
       <c r="C71" t="n">
-        <v>0.003292080288896853</v>
+        <v>0.003364437250544123</v>
       </c>
       <c r="D71" t="n">
-        <v>1.014363094348874</v>
+        <v>0.995465506193988</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -1945,17 +1945,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5035697165404435</v>
+        <v>0.5029851358227058</v>
       </c>
       <c r="C72" t="n">
-        <v>0.003460520950933457</v>
+        <v>0.00344653530200954</v>
       </c>
       <c r="D72" t="n">
-        <v>1.066263405448175</v>
+        <v>1.019756575479451</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -1964,17 +1964,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CB_YN</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.503129107726445</v>
+        <v>0.5026231660116858</v>
       </c>
       <c r="C73" t="n">
-        <v>0.003265837539623402</v>
+        <v>0.003541877642527643</v>
       </c>
       <c r="D73" t="n">
-        <v>1.006277120125517</v>
+        <v>1.047966348525515</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -1983,17 +1983,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_AMT</t>
+          <t>ETI_EXE_CNT</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5031060898409222</v>
+        <v>0.5024564770680318</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003332726814101617</v>
+        <v>0.003393903363231166</v>
       </c>
       <c r="D74" t="n">
-        <v>1.026887192020577</v>
+        <v>1.004183902941269</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
@@ -2002,17 +2002,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VNCL_GOEM_VRSC_YN</t>
+          <t>PRIV_AID_BZR_YN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5027770286344506</v>
+        <v>0.5020016435310042</v>
       </c>
       <c r="C75" t="n">
-        <v>0.003263533460838379</v>
+        <v>0.003395847673368985</v>
       </c>
       <c r="D75" t="n">
-        <v>1.005567182250101</v>
+        <v>1.004759183004891</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -2021,17 +2021,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
+          <t>NTS_BT_CD</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5019247576720666</v>
+        <v>0.5018923297373296</v>
       </c>
       <c r="C76" t="n">
-        <v>0.003258027815122984</v>
+        <v>0.003426657832646834</v>
       </c>
       <c r="D76" t="n">
-        <v>1.003870770457505</v>
+        <v>1.013875254584612</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -2040,17 +2040,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LSA_MNG_CMMT_DLBR_YN</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5018066048130083</v>
+        <v>0.5016177676253643</v>
       </c>
       <c r="C77" t="n">
-        <v>0.003264822394257026</v>
+        <v>0.003277690748716212</v>
       </c>
       <c r="D77" t="n">
-        <v>1.005964331279351</v>
+        <v>0.9697990592008948</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -2059,17 +2059,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TMNT_DLNG_AMT</t>
+          <t>TMNT_CORP_CLT_NUM</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.501789880728077</v>
+        <v>0.5014282297387833</v>
       </c>
       <c r="C78" t="n">
-        <v>0.003326103108533695</v>
+        <v>0.003524319120668061</v>
       </c>
       <c r="D78" t="n">
-        <v>1.024846281141643</v>
+        <v>1.042771154931657</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
@@ -2078,17 +2078,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SBAT_EXE_SUM_AMT</t>
+          <t>PBCN_DGR</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5017894189501502</v>
+        <v>0.5009032935756651</v>
       </c>
       <c r="C79" t="n">
-        <v>0.003326097916930697</v>
+        <v>0.003385859124663081</v>
       </c>
       <c r="D79" t="n">
-        <v>1.024844681493391</v>
+        <v>1.001803783645887</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -2097,17 +2097,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PBCN_DGR</t>
+          <t>PRIV_AID_BIZ_CGP_YN</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5012132085496424</v>
+        <v>0.5005674131386064</v>
       </c>
       <c r="C80" t="n">
-        <v>0.003253334018405725</v>
+        <v>0.003383589897530648</v>
       </c>
       <c r="D80" t="n">
-        <v>1.002424507382324</v>
+        <v>1.001132367546302</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AST_LAT_RT</t>
+          <t>INVC_EXE_CNT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5008661006299149</v>
+        <v>0.500434703823276</v>
       </c>
       <c r="C81" t="n">
-        <v>0.003250909419827864</v>
+        <v>0.003382719996814736</v>
       </c>
       <c r="D81" t="n">
-        <v>1.001677434680516</v>
+        <v>1.000874982405187</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>VNCL_GOEM_VRSC_YN</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5008418452459913</v>
+        <v>0.5001709073601995</v>
       </c>
       <c r="C82" t="n">
-        <v>0.003115840495814372</v>
+        <v>0.003380914511253847</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9600596976603148</v>
+        <v>1.000340777584603</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
@@ -2154,17 +2154,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TMNT_CORP_DLNG_AMT</t>
+          <t>RERE_DSCRD_CNT</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5003170213436747</v>
+        <v>0.5000880284563254</v>
       </c>
       <c r="C83" t="n">
-        <v>0.003231417296628579</v>
+        <v>0.003395477247430739</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9956714783645235</v>
+        <v>1.004649581839327</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -2173,17 +2173,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RERE_DSCRD_CNT</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0.500194525612712</v>
-      </c>
+          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>0.003323987596027563</v>
+        <v>0.003379762763862648</v>
       </c>
       <c r="D84" t="n">
-        <v>1.024194444727115</v>
+        <v>1</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -2278,13 +2276,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999082090604214</v>
+        <v>0.999858572159023</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1924</v>
+        <v>893</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2299,13 +2297,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9968577994433535</v>
+        <v>0.9967834232064955</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2320,7 +2318,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9967545346363276</v>
+        <v>0.9966202372361374</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">

--- a/outputs/reports/comparison/leakage_audit.xlsx
+++ b/outputs/reports/comparison/leakage_audit.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003379762763862648</v>
+        <v>0.003220878504856724</v>
       </c>
     </row>
     <row r="4">
@@ -615,17 +615,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6053013709396988</v>
+        <v>0.5947854320303076</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004713153125455861</v>
+        <v>0.004341230507262236</v>
       </c>
       <c r="D2" t="n">
-        <v>1.39452188060363</v>
+        <v>1.347840503985527</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -634,17 +634,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5991175197519107</v>
+        <v>0.584455681428754</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004417100539164517</v>
+        <v>0.004511780036038296</v>
       </c>
       <c r="D3" t="n">
-        <v>1.306926209849215</v>
+        <v>1.400791749591001</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -653,17 +653,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5980091127479635</v>
+        <v>0.5698519177672139</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005085482275452633</v>
+        <v>0.003809007467343742</v>
       </c>
       <c r="D4" t="n">
-        <v>1.504686166090711</v>
+        <v>1.182598928087534</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -672,17 +672,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.591860654484926</v>
+        <v>0.5642504586834541</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004655132952401041</v>
+        <v>0.003763991629215125</v>
       </c>
       <c r="D5" t="n">
-        <v>1.377354944014119</v>
+        <v>1.168622667244184</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -691,17 +691,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_CNT</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5726737968486489</v>
+        <v>0.5622456654364937</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004425600632325504</v>
+        <v>0.003657444588748417</v>
       </c>
       <c r="D6" t="n">
-        <v>1.309441206834173</v>
+        <v>1.1355425494111</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -710,17 +710,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_AMT</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5706553225969345</v>
+        <v>0.5613471030821162</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004098844419317701</v>
+        <v>0.005405113714185033</v>
       </c>
       <c r="D7" t="n">
-        <v>1.212760985221706</v>
+        <v>1.678148898207345</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -729,17 +729,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.568511896543703</v>
+        <v>0.5584572710602458</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003969343101247478</v>
+        <v>0.003903897689899899</v>
       </c>
       <c r="D8" t="n">
-        <v>1.174444296412986</v>
+        <v>1.212059903536647</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -748,17 +748,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>CUMU_PYHWY_EXE_CNT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5579909450956826</v>
+        <v>0.5498645744484159</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003959733708587523</v>
+        <v>0.003790866184364951</v>
       </c>
       <c r="D9" t="n">
-        <v>1.171601081272947</v>
+        <v>1.176966525948976</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -767,17 +767,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AID_BIZ_EXE_TY_CD</t>
+          <t>OPCT_YN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5429081753513888</v>
+        <v>0.5477792251048382</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003712512236963653</v>
+        <v>0.003650935313917074</v>
       </c>
       <c r="D10" t="n">
-        <v>1.098453499949421</v>
+        <v>1.133521586862675</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -786,17 +786,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TMNT_CLT_NUM</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5392673636857247</v>
+        <v>0.5456611003287205</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003762360171311574</v>
+        <v>0.00358350124865237</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11320244472179</v>
+        <v>1.112585042636303</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,17 +805,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>LBST_EXE_CNT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5392340614246112</v>
+        <v>0.5456146297614042</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003703497033318717</v>
+        <v>0.003705043862936348</v>
       </c>
       <c r="D12" t="n">
-        <v>1.095786092715597</v>
+        <v>1.150320900757218</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -824,17 +824,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_AMT</t>
+          <t>LBST_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5386703962544304</v>
+        <v>0.5400722137385333</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003841486014310072</v>
+        <v>0.003556796148633358</v>
       </c>
       <c r="D13" t="n">
-        <v>1.136614100665377</v>
+        <v>1.104293795394675</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -843,17 +843,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5386570597334498</v>
+        <v>0.5378176941233365</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003786533084775968</v>
+        <v>0.003565696419167699</v>
       </c>
       <c r="D14" t="n">
-        <v>1.120354696271176</v>
+        <v>1.1070571006609</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -862,17 +862,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5311851801549257</v>
+        <v>0.5377224097942416</v>
       </c>
       <c r="C15" t="n">
-        <v>0.005920462364369126</v>
+        <v>0.003501365673743107</v>
       </c>
       <c r="D15" t="n">
-        <v>1.751739035553719</v>
+        <v>1.087084057490352</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -881,17 +881,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5311725776110954</v>
+        <v>0.5354903007419378</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003813109567881095</v>
+        <v>0.003685645228250556</v>
       </c>
       <c r="D16" t="n">
-        <v>1.128218113014295</v>
+        <v>1.144298123227255</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -900,17 +900,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5304939805987352</v>
+        <v>0.5337781921494024</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003661609091067947</v>
+        <v>0.00357417765381151</v>
       </c>
       <c r="D17" t="n">
-        <v>1.083392340497646</v>
+        <v>1.109690306052231</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -919,17 +919,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AID_BIZ_DV_CD</t>
+          <t>LODI_CNT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5301924018810366</v>
+        <v>0.5337507951850081</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003601817248134569</v>
+        <v>0.003507962508569756</v>
       </c>
       <c r="D18" t="n">
-        <v>1.06570120442955</v>
+        <v>1.08913220516705</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -938,17 +938,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>TMNT_CLT_NUM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5276197729290206</v>
+        <v>0.5336489938463154</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003942193601391267</v>
+        <v>0.003564941815343477</v>
       </c>
       <c r="D19" t="n">
-        <v>1.166411336186754</v>
+        <v>1.106822815566605</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -957,17 +957,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_DLNG_AMT</t>
+          <t>TMNT_INDV_BZR_CLT_NUM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5258162251458354</v>
+        <v>0.5333182561322518</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003691196013812182</v>
+        <v>0.003545508916346873</v>
       </c>
       <c r="D20" t="n">
-        <v>1.092146482374285</v>
+        <v>1.100789399848719</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -976,17 +976,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TMNT_EXE_AMT</t>
+          <t>AID_BIZ_EXE_TY_CD</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5255621050783239</v>
+        <v>0.5319371664371152</v>
       </c>
       <c r="C21" t="n">
-        <v>0.003726397731192884</v>
+        <v>0.00344966768249136</v>
       </c>
       <c r="D21" t="n">
-        <v>1.102561922699591</v>
+        <v>1.071033159831905</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LBST_EXE_CNT</t>
+          <t>AID_BIZ_DPI_DV_CD</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5249994745035937</v>
+        <v>0.5317551303541883</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003674031827674029</v>
+        <v>0.003439693285696431</v>
       </c>
       <c r="D22" t="n">
-        <v>1.087067964342878</v>
+        <v>1.067936365966539</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -1014,17 +1014,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5248864322621625</v>
+        <v>0.5284505324095575</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00370626485744985</v>
+        <v>0.00363381578642965</v>
       </c>
       <c r="D23" t="n">
-        <v>1.096605033074585</v>
+        <v>1.12820641354533</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -1033,17 +1033,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TMNT_EXE_CNT</t>
+          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5244747491636994</v>
+        <v>0.5272340157221905</v>
       </c>
       <c r="C24" t="n">
-        <v>0.003608641685081744</v>
+        <v>0.003470598386898386</v>
       </c>
       <c r="D24" t="n">
-        <v>1.067720410339546</v>
+        <v>1.07753160563651</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1052,17 +1052,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PBAC_TY_DV_CD</t>
+          <t>PRIV_AID_BIZ_CGP_YN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5233045943799433</v>
+        <v>0.5265017553183537</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003610546976529176</v>
+        <v>0.003403837161971784</v>
       </c>
       <c r="D25" t="n">
-        <v>1.068284145601619</v>
+        <v>1.056803961043293</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1071,17 +1071,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LBST_EXE_SUM_AMT</t>
+          <t>PBAC_TY_DV_CD</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5219652637193175</v>
+        <v>0.5255392965615575</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003577588124866324</v>
+        <v>0.003395272481664479</v>
       </c>
       <c r="D26" t="n">
-        <v>1.058532321593361</v>
+        <v>1.054144847917979</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -1090,17 +1090,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>NTS_BT_CD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5210444640077985</v>
+        <v>0.5242792993903789</v>
       </c>
       <c r="C27" t="n">
-        <v>0.004005418475789617</v>
+        <v>0.003417323569526058</v>
       </c>
       <c r="D27" t="n">
-        <v>1.185118233331834</v>
+        <v>1.060991143991652</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1109,17 +1109,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EXE_PLAN_CHG_TMS</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5209092384782492</v>
+        <v>0.5233797604260239</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00354088536532958</v>
+        <v>0.003979462412441149</v>
       </c>
       <c r="D28" t="n">
-        <v>1.047672754783175</v>
+        <v>1.235520807891563</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -1128,17 +1128,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_CNT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5202057682295993</v>
+        <v>0.5230576569651261</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003554389869566619</v>
+        <v>0.003317659290224514</v>
       </c>
       <c r="D29" t="n">
-        <v>1.05166845068865</v>
+        <v>1.030047946615141</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1147,17 +1147,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACNT_DV_CD</t>
+          <t>FYR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5198670436310843</v>
+        <v>0.5225675744959367</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003707011892182272</v>
+        <v>0.003522415166320156</v>
       </c>
       <c r="D30" t="n">
-        <v>1.096826064781428</v>
+        <v>1.093619383968923</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1166,17 +1166,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CARD_RTRCN_CNT</t>
+          <t>CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5193578040378144</v>
+        <v>0.522390312253299</v>
       </c>
       <c r="C31" t="n">
-        <v>0.003686580453424638</v>
+        <v>0.003442416494801953</v>
       </c>
       <c r="D31" t="n">
-        <v>1.090780836111507</v>
+        <v>1.068781852408023</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1185,17 +1185,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AID_BIZ_DPI_DV_CD</t>
+          <t>CONT_BIZ_YN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5193508566317592</v>
+        <v>0.5221640910545116</v>
       </c>
       <c r="C32" t="n">
-        <v>0.003515958794429289</v>
+        <v>0.003373762866696996</v>
       </c>
       <c r="D32" t="n">
-        <v>1.040297512009685</v>
+        <v>1.047466665262207</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -1204,17 +1204,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OPCT_YN</t>
+          <t>AID_BIZ_DV_CD</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5191210495573407</v>
+        <v>0.5220846893995945</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003529328021352844</v>
+        <v>0.003374384128634491</v>
       </c>
       <c r="D33" t="n">
-        <v>1.044253182232016</v>
+        <v>1.047659551127526</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1223,17 +1223,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CARD_FR_USE_CNT</t>
+          <t>ETC_EXE_CNT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5190472848537676</v>
+        <v>0.5220721164875944</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003574500392280498</v>
+        <v>0.003454045708876738</v>
       </c>
       <c r="D34" t="n">
-        <v>1.057618727118968</v>
+        <v>1.072392424510401</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -1242,17 +1242,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_AMT</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5172821244659399</v>
+        <v>0.521451849481506</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00364255759657843</v>
+        <v>0.003569181799801592</v>
       </c>
       <c r="D35" t="n">
-        <v>1.077755408020248</v>
+        <v>1.108139221774328</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -1261,17 +1261,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>TMNT_CORP_CLT_NUM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5162397636930894</v>
+        <v>0.5213734759031593</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003685178258303364</v>
+        <v>0.003624816855234848</v>
       </c>
       <c r="D36" t="n">
-        <v>1.090365956364246</v>
+        <v>1.125412476679586</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -1280,17 +1280,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_CNT</t>
+          <t>ODN_CAPT_DV_CD</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5161191610966001</v>
+        <v>0.5210257416606934</v>
       </c>
       <c r="C37" t="n">
-        <v>0.003524130313308992</v>
+        <v>0.003362009453971953</v>
       </c>
       <c r="D37" t="n">
-        <v>1.042715290845251</v>
+        <v>1.043817532670798</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -1299,17 +1299,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5160412814360266</v>
+        <v>0.5205222146948495</v>
       </c>
       <c r="C38" t="n">
-        <v>0.003555484379227469</v>
+        <v>0.003383878629699417</v>
       </c>
       <c r="D38" t="n">
-        <v>1.051992292844836</v>
+        <v>1.050607349701923</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -1318,17 +1318,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>CARD_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5159831196030913</v>
+        <v>0.5199060357262425</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003632429231696977</v>
+        <v>0.003422760764030299</v>
       </c>
       <c r="D39" t="n">
-        <v>1.074758640025243</v>
+        <v>1.062679253150704</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -1337,17 +1337,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5148346932758682</v>
+        <v>0.5195471202619161</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003832274560480501</v>
+        <v>0.003522506227733464</v>
       </c>
       <c r="D40" t="n">
-        <v>1.133888627171183</v>
+        <v>1.0936476561975</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -1356,17 +1356,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETC_EXE_CNT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5130669971531525</v>
+        <v>0.5193890098681585</v>
       </c>
       <c r="C41" t="n">
-        <v>0.003562915883614338</v>
+        <v>0.003429165411120457</v>
       </c>
       <c r="D41" t="n">
-        <v>1.054191117113311</v>
+        <v>1.064667731474397</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -1375,17 +1375,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FLD_CD</t>
+          <t>TMNT_EXE_CNT</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5123974167377492</v>
+        <v>0.5193318560078047</v>
       </c>
       <c r="C42" t="n">
-        <v>0.003591840932793936</v>
+        <v>0.00340002232224683</v>
       </c>
       <c r="D42" t="n">
-        <v>1.062749424663437</v>
+        <v>1.055619551349105</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -1394,17 +1394,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>INDV_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5121086201540349</v>
+        <v>0.5184681382103629</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003504634640979259</v>
+        <v>0.003401948461559931</v>
       </c>
       <c r="D43" t="n">
-        <v>1.03694693558133</v>
+        <v>1.056217568104532</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -1413,17 +1413,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LBST_EXE_AVG_AMT</t>
+          <t>INDV_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5112794934077218</v>
+        <v>0.5184118730901945</v>
       </c>
       <c r="C44" t="n">
-        <v>0.003477768306317458</v>
+        <v>0.003406167626284526</v>
       </c>
       <c r="D44" t="n">
-        <v>1.028997757920382</v>
+        <v>1.057527510320059</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -1432,17 +1432,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LODI_CNT</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5112744687875515</v>
+        <v>0.5174884883563382</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003472628611154502</v>
+        <v>0.003350371253806113</v>
       </c>
       <c r="D45" t="n">
-        <v>1.027477031312612</v>
+        <v>1.040204170618087</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -1451,17 +1451,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ODN_CAPT_DV_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5112051235634134</v>
+        <v>0.5171348802274687</v>
       </c>
       <c r="C46" t="n">
-        <v>0.003457070541255674</v>
+        <v>0.0160308013768529</v>
       </c>
       <c r="D46" t="n">
-        <v>1.022873728955068</v>
+        <v>4.977151839996526</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -1470,17 +1470,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TMNT_INDV_CLT_NUM</t>
+          <t>TMNT_INDV_BZR_DLNG_AMT</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5109887681819218</v>
+        <v>0.5164120695921558</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003400932694737213</v>
+        <v>0.003488027150197082</v>
       </c>
       <c r="D47" t="n">
-        <v>1.006263732798325</v>
+        <v>1.082942788725973</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -1489,17 +1489,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TMNT_CORP_DLNG_AMT</t>
+          <t>EXE_PLAN_CHG_TMS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5108315487147428</v>
+        <v>0.5159538181644527</v>
       </c>
       <c r="C48" t="n">
-        <v>0.003487936561209469</v>
+        <v>0.003330867687137105</v>
       </c>
       <c r="D48" t="n">
-        <v>1.032006328522062</v>
+        <v>1.034148814404061</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -1508,17 +1508,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_CNT</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.510711457559778</v>
+        <v>0.5155481869342464</v>
       </c>
       <c r="C49" t="n">
-        <v>0.003470270349330065</v>
+        <v>0.003455156573530645</v>
       </c>
       <c r="D49" t="n">
-        <v>1.026779271739173</v>
+        <v>1.0727373194365</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -1527,17 +1527,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
+          <t>ACNT_DV_CD</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5106342786912175</v>
+        <v>0.5152422724365169</v>
       </c>
       <c r="C50" t="n">
-        <v>0.003540885449090136</v>
+        <v>0.003436104300362244</v>
       </c>
       <c r="D50" t="n">
-        <v>1.047672779566145</v>
+        <v>1.066822078256284</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -1546,17 +1546,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TMNT_DLNG_AMT</t>
+          <t>TMNT_EXE_AMT</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5099484434148358</v>
+        <v>0.5145113246400066</v>
       </c>
       <c r="C51" t="n">
-        <v>0.003535529976933765</v>
+        <v>0.003454049901810517</v>
       </c>
       <c r="D51" t="n">
-        <v>1.046088209130127</v>
+        <v>1.072393726308582</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1565,17 +1565,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SBAT_EXE_SUM_AMT</t>
+          <t>INDV_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5099484434148358</v>
+        <v>0.5129590181439447</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003535529976933765</v>
+        <v>0.003368541332843181</v>
       </c>
       <c r="D52" t="n">
-        <v>1.046088209130127</v>
+        <v>1.045845513192689</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -1584,17 +1584,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_AMT</t>
+          <t>LBST_EXE_RT_DV_CD</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5095566206448938</v>
+        <v>0.5127959226039689</v>
       </c>
       <c r="C53" t="n">
-        <v>0.003469396132173391</v>
+        <v>0.00336061685656902</v>
       </c>
       <c r="D53" t="n">
-        <v>1.026520609454938</v>
+        <v>1.043385166966586</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -1603,17 +1603,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CUMU_EXE_CNT</t>
+          <t>INDV_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5092080498209948</v>
+        <v>0.5110227382293486</v>
       </c>
       <c r="C54" t="n">
-        <v>0.003443484870956673</v>
+        <v>0.003384696063587407</v>
       </c>
       <c r="D54" t="n">
-        <v>1.018854017736203</v>
+        <v>1.050861141916301</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -1622,17 +1622,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5089980425610237</v>
+        <v>0.5103453240577478</v>
       </c>
       <c r="C55" t="n">
-        <v>0.003539635487016026</v>
+        <v>0.003442118773615348</v>
       </c>
       <c r="D55" t="n">
-        <v>1.047302942343404</v>
+        <v>1.068689417630941</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1641,17 +1641,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TMNT_INDV_DLNG_AMT</t>
+          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5088921761174736</v>
+        <v>0.5090919401345113</v>
       </c>
       <c r="C56" t="n">
-        <v>0.003409107204659028</v>
+        <v>0.003449496554619375</v>
       </c>
       <c r="D56" t="n">
-        <v>1.008682396619709</v>
+        <v>1.070980029025597</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -1660,17 +1660,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5083820346693013</v>
+        <v>0.508955391314082</v>
       </c>
       <c r="C57" t="n">
-        <v>0.003759197532156529</v>
+        <v>0.003328207626318328</v>
       </c>
       <c r="D57" t="n">
-        <v>1.112266686984927</v>
+        <v>1.033322933882717</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -1679,17 +1679,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EVENT_FSTV_YN</t>
+          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5083207143921409</v>
+        <v>0.5088376001837501</v>
       </c>
       <c r="C58" t="n">
-        <v>0.00347603697691705</v>
+        <v>0.003323761544149857</v>
       </c>
       <c r="D58" t="n">
-        <v>1.028485494332263</v>
+        <v>1.031942539632587</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -1698,17 +1698,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LBST_EXE_RT_DV_CD</t>
+          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5081886180258135</v>
+        <v>0.508790845504105</v>
       </c>
       <c r="C59" t="n">
-        <v>0.003467506790545416</v>
+        <v>0.003291374881933087</v>
       </c>
       <c r="D59" t="n">
-        <v>1.025961593405594</v>
+        <v>1.021887313343258</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -1717,17 +1717,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CONT_BIZ_YN</t>
+          <t>EVENT_FSTV_YN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5077011732593509</v>
+        <v>0.5082246071227563</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003432923477272989</v>
+        <v>0.00331255169934613</v>
       </c>
       <c r="D60" t="n">
-        <v>1.015729125718157</v>
+        <v>1.028462170911189</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -1736,17 +1736,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>TMNT_INDV_DLNG_AMT</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5062201674401771</v>
+        <v>0.5081502399885123</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003750715992288435</v>
+        <v>0.003281209816039916</v>
       </c>
       <c r="D61" t="n">
-        <v>1.109757179525179</v>
+        <v>1.018731321623035</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -1759,13 +1759,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5054898718883488</v>
+        <v>0.5081175164409926</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00326429030523436</v>
+        <v>0.003134935180660066</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9658341526621479</v>
+        <v>0.9733168065585012</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -1774,17 +1774,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NTN_DRCT_BIZ_YN</t>
+          <t>TMNT_INDV_CLT_NUM</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5048388556290527</v>
+        <v>0.507794831365755</v>
       </c>
       <c r="C63" t="n">
-        <v>0.003441631452218206</v>
+        <v>0.003274051402958515</v>
       </c>
       <c r="D63" t="n">
-        <v>1.018305630506696</v>
+        <v>1.016508818330655</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -1793,17 +1793,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AST_LAT_RT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5043124573678353</v>
+        <v>0.5070155175249794</v>
       </c>
       <c r="C64" t="n">
-        <v>0.00340983073402057</v>
+        <v>0.003477346580887464</v>
       </c>
       <c r="D64" t="n">
-        <v>1.008896473586672</v>
+        <v>1.07962674644325</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -1812,17 +1812,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LSA_MNG_CMMT_DLBR_YN</t>
+          <t>INVC_EXE_CNT</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5041542931002821</v>
+        <v>0.5063388201198276</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003448634527748728</v>
+        <v>0.003267519380533657</v>
       </c>
       <c r="D65" t="n">
-        <v>1.020377691778392</v>
+        <v>1.01448079323905</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -1831,17 +1831,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CB_YN</t>
+          <t>CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5040480011061503</v>
+        <v>0.5058617515853102</v>
       </c>
       <c r="C66" t="n">
-        <v>0.003407254674007619</v>
+        <v>0.003285768557352733</v>
       </c>
       <c r="D66" t="n">
-        <v>1.008134272156295</v>
+        <v>1.020146693642173</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -1850,17 +1850,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
+          <t>TMNT_CORP_DLNG_AMT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5036704147600245</v>
+        <v>0.5058241424773369</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00347492282233829</v>
+        <v>0.003237579151372644</v>
       </c>
       <c r="D67" t="n">
-        <v>1.028155839662215</v>
+        <v>1.005185121540827</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -1869,17 +1869,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>PRIV_AID_BZR_YN</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.503590893411198</v>
+        <v>0.505148853081</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003649796631633055</v>
+        <v>0.003254298073168384</v>
       </c>
       <c r="D68" t="n">
-        <v>1.079897284702253</v>
+        <v>1.010375917086369</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -1888,17 +1888,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CUMU_EXE_AMT</t>
+          <t>CORP_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5031595451909028</v>
+        <v>0.5046052679505422</v>
       </c>
       <c r="C69" t="n">
-        <v>0.003546758732446809</v>
+        <v>0.003297485575643109</v>
       </c>
       <c r="D69" t="n">
-        <v>1.049410559335622</v>
+        <v>1.023784526696946</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
@@ -1907,17 +1907,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
+          <t>SBAT_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5031053519099514</v>
+        <v>0.5042446612019271</v>
       </c>
       <c r="C70" t="n">
-        <v>0.003368428979121521</v>
+        <v>0.003286391102475304</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9966465738772226</v>
+        <v>1.02033997790348</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -1926,17 +1926,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
+          <t>TMNT_DLNG_AMT</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.502994390571823</v>
+        <v>0.5042446612019271</v>
       </c>
       <c r="C71" t="n">
-        <v>0.003364437250544123</v>
+        <v>0.003286391102475304</v>
       </c>
       <c r="D71" t="n">
-        <v>0.995465506193988</v>
+        <v>1.02033997790348</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -1945,17 +1945,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>ETI_EXE_CNT</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5029851358227058</v>
+        <v>0.5040588191017096</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00344653530200954</v>
+        <v>0.003263138153769021</v>
       </c>
       <c r="D72" t="n">
-        <v>1.019756575479451</v>
+        <v>1.013120534925044</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -1964,17 +1964,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>LSA_MNG_CMMT_DLBR_YN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5026231660116858</v>
+        <v>0.5039181044162684</v>
       </c>
       <c r="C73" t="n">
-        <v>0.003541877642527643</v>
+        <v>0.003282289210406969</v>
       </c>
       <c r="D73" t="n">
-        <v>1.047966348525515</v>
+        <v>1.019066445833845</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -1983,17 +1983,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ETI_EXE_CNT</t>
+          <t>CB_YN</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5024564770680318</v>
+        <v>0.5033859038634763</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003393903363231166</v>
+        <v>0.003242767323660943</v>
       </c>
       <c r="D74" t="n">
-        <v>1.004183902941269</v>
+        <v>1.006795915701636</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
@@ -2002,17 +2002,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PRIV_AID_BZR_YN</t>
+          <t>AST_LAT_RT</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5020016435310042</v>
+        <v>0.5032420313050697</v>
       </c>
       <c r="C75" t="n">
-        <v>0.003395847673368985</v>
+        <v>0.003242169745757363</v>
       </c>
       <c r="D75" t="n">
-        <v>1.004759183004891</v>
+        <v>1.006610383120175</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -2021,17 +2021,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NTS_BT_CD</t>
+          <t>NTN_DRCT_BIZ_YN</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5018923297373296</v>
+        <v>0.5029387252848896</v>
       </c>
       <c r="C76" t="n">
-        <v>0.003426657832646834</v>
+        <v>0.003250350701130647</v>
       </c>
       <c r="D76" t="n">
-        <v>1.013875254584612</v>
+        <v>1.009150359515108</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -2040,17 +2040,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>VNCL_GOEM_VRSC_YN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5016177676253643</v>
+        <v>0.5025320500778649</v>
       </c>
       <c r="C77" t="n">
-        <v>0.003277690748716212</v>
+        <v>0.003237220244588723</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9697990592008948</v>
+        <v>1.005073690208233</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -2059,17 +2059,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TMNT_CORP_CLT_NUM</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5014282297387833</v>
+        <v>0.5024154615084052</v>
       </c>
       <c r="C78" t="n">
-        <v>0.003524319120668061</v>
+        <v>0.003275007452927767</v>
       </c>
       <c r="D78" t="n">
-        <v>1.042771154931657</v>
+        <v>1.016805647275867</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
@@ -2078,17 +2078,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PBCN_DGR</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5009032935756651</v>
+        <v>0.5022950669216547</v>
       </c>
       <c r="C79" t="n">
-        <v>0.003385859124663081</v>
+        <v>0.003203771771735847</v>
       </c>
       <c r="D79" t="n">
-        <v>1.001803783645887</v>
+        <v>0.9946887990046561</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -2097,17 +2097,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PRIV_AID_BIZ_CGP_YN</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5005674131386064</v>
+        <v>0.502285083657963</v>
       </c>
       <c r="C80" t="n">
-        <v>0.003383589897530648</v>
+        <v>0.003210006618193271</v>
       </c>
       <c r="D80" t="n">
-        <v>1.001132367546302</v>
+        <v>0.9966245585957189</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>INVC_EXE_CNT</t>
+          <t>RERE_DSCRD_CNT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.500434703823276</v>
+        <v>0.5021200110476598</v>
       </c>
       <c r="C81" t="n">
-        <v>0.003382719996814736</v>
+        <v>0.003437055272839824</v>
       </c>
       <c r="D81" t="n">
-        <v>1.000874982405187</v>
+        <v>1.067117330770822</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VNCL_GOEM_VRSC_YN</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5001709073601995</v>
+        <v>0.5014156656215643</v>
       </c>
       <c r="C82" t="n">
-        <v>0.003380914511253847</v>
+        <v>0.003269976159089338</v>
       </c>
       <c r="D82" t="n">
-        <v>1.000340777584603</v>
+        <v>1.015243559842006</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
@@ -2154,17 +2154,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RERE_DSCRD_CNT</t>
+          <t>PBCN_DGR</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5000880284563254</v>
+        <v>0.5011246228769732</v>
       </c>
       <c r="C83" t="n">
-        <v>0.003395477247430739</v>
+        <v>0.003228116227310739</v>
       </c>
       <c r="D83" t="n">
-        <v>1.004649581839327</v>
+        <v>1.002247126814346</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -2176,12 +2176,14 @@
           <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="n">
+        <v>0.5009446002675736</v>
+      </c>
       <c r="C84" t="n">
-        <v>0.003379762763862648</v>
+        <v>0.003227025328135209</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>1.001908430656175</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -2276,13 +2278,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.999858572159023</v>
+        <v>0.9999098481843425</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>893</v>
+        <v>1910</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2297,13 +2299,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9967834232064955</v>
+        <v>0.9968807471782481</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2318,7 +2320,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9966202372361374</v>
+        <v>0.9967791214951432</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">

--- a/outputs/reports/comparison/leakage_audit.xlsx
+++ b/outputs/reports/comparison/leakage_audit.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003220878504856724</v>
+        <v>0.003245465363672425</v>
       </c>
     </row>
     <row r="4">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5947854320303076</v>
+        <v>0.5953456177723242</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004341230507262236</v>
+        <v>0.004388227477903696</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347840503985527</v>
+        <v>1.352110402108304</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.584455681428754</v>
+        <v>0.5865129899625758</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004511780036038296</v>
+        <v>0.00451154947971646</v>
       </c>
       <c r="D3" t="n">
-        <v>1.400791749591001</v>
+        <v>1.390108651355746</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -653,17 +653,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5698519177672139</v>
+        <v>0.5665283492279621</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003809007467343742</v>
+        <v>0.003816934440223919</v>
       </c>
       <c r="D4" t="n">
-        <v>1.182598928087534</v>
+        <v>1.176082321798328</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -672,17 +672,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5642504586834541</v>
+        <v>0.5639898417659797</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003763991629215125</v>
+        <v>0.004020446872672561</v>
       </c>
       <c r="D5" t="n">
-        <v>1.168622667244184</v>
+        <v>1.238789024734253</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -691,17 +691,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5622456654364937</v>
+        <v>0.5635780338585543</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003657444588748417</v>
+        <v>0.003781455584011756</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1355425494111</v>
+        <v>1.165150497780333</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -710,17 +710,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5613471030821162</v>
+        <v>0.5598697291247227</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005405113714185033</v>
+        <v>0.003659745890894433</v>
       </c>
       <c r="D7" t="n">
-        <v>1.678148898207345</v>
+        <v>1.127649036671039</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -729,17 +729,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5584572710602458</v>
+        <v>0.55683852371723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003903897689899899</v>
+        <v>0.005400036456637725</v>
       </c>
       <c r="D8" t="n">
-        <v>1.212059903536647</v>
+        <v>1.663871233100231</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5498645744484159</v>
+        <v>0.5476144328059797</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003790866184364951</v>
+        <v>0.003792557774419537</v>
       </c>
       <c r="D9" t="n">
-        <v>1.176966525948976</v>
+        <v>1.168571329360313</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5477792251048382</v>
+        <v>0.5464846449371249</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003650935313917074</v>
+        <v>0.003663743761293497</v>
       </c>
       <c r="D10" t="n">
-        <v>1.133521586862675</v>
+        <v>1.128880869382555</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -786,17 +786,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_AMT</t>
+          <t>LBST_EXE_CNT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5456611003287205</v>
+        <v>0.5444679008528904</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00358350124865237</v>
+        <v>0.00369384421156972</v>
       </c>
       <c r="D11" t="n">
-        <v>1.112585042636303</v>
+        <v>1.138155487011554</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,17 +805,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LBST_EXE_CNT</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5456146297614042</v>
+        <v>0.5435407363211828</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003705043862936348</v>
+        <v>0.003560921462815187</v>
       </c>
       <c r="D12" t="n">
-        <v>1.150320900757218</v>
+        <v>1.097199034281422</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -824,17 +824,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LBST_EXE_SUM_AMT</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5400722137385333</v>
+        <v>0.5420107215366481</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003556796148633358</v>
+        <v>0.00380586140159499</v>
       </c>
       <c r="D13" t="n">
-        <v>1.104293795394675</v>
+        <v>1.172670472529229</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -843,17 +843,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>LBST_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5378176941233365</v>
+        <v>0.5408115195586706</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003565696419167699</v>
+        <v>0.003580103909639817</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1070571006609</v>
+        <v>1.103109572424686</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -862,17 +862,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5377224097942416</v>
+        <v>0.5396393502764638</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003501365673743107</v>
+        <v>0.004214741324079186</v>
       </c>
       <c r="D15" t="n">
-        <v>1.087084057490352</v>
+        <v>1.29865546286711</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -881,17 +881,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5354903007419378</v>
+        <v>0.5392026379213561</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003685645228250556</v>
+        <v>0.003522438628760229</v>
       </c>
       <c r="D16" t="n">
-        <v>1.144298123227255</v>
+        <v>1.085341617934999</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -900,17 +900,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LBST_EXE_AVG_AMT</t>
+          <t>AID_BIZ_EXE_TY_CD</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5337781921494024</v>
+        <v>0.5368930610192355</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00357417765381151</v>
+        <v>0.003517556737091153</v>
       </c>
       <c r="D17" t="n">
-        <v>1.109690306052231</v>
+        <v>1.083837398625275</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -919,17 +919,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LODI_CNT</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5337507951850081</v>
+        <v>0.5362428540281104</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003507962508569756</v>
+        <v>0.003583608447263103</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08913220516705</v>
+        <v>1.104189398345035</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -938,17 +938,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TMNT_CLT_NUM</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5336489938463154</v>
+        <v>0.5339217389068401</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003564941815343477</v>
+        <v>0.003611332294837258</v>
       </c>
       <c r="D19" t="n">
-        <v>1.106822815566605</v>
+        <v>1.112731731868133</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -957,17 +957,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>LODI_CNT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5333182561322518</v>
+        <v>0.5325959425035319</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003545508916346873</v>
+        <v>0.003522441688832761</v>
       </c>
       <c r="D20" t="n">
-        <v>1.100789399848719</v>
+        <v>1.085342560811348</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -976,17 +976,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AID_BIZ_EXE_TY_CD</t>
+          <t>TMNT_CLT_NUM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5319371664371152</v>
+        <v>0.5323037213752917</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00344966768249136</v>
+        <v>0.003614848678399931</v>
       </c>
       <c r="D21" t="n">
-        <v>1.071033159831905</v>
+        <v>1.11381520778565</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5317551303541883</v>
+        <v>0.5292940530079201</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003439693285696431</v>
+        <v>0.003447784372087854</v>
       </c>
       <c r="D22" t="n">
-        <v>1.067936365966539</v>
+        <v>1.062338982470759</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -1014,17 +1014,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5284505324095575</v>
+        <v>0.5283204087837603</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00363381578642965</v>
+        <v>0.003597886647225243</v>
       </c>
       <c r="D23" t="n">
-        <v>1.12820641354533</v>
+        <v>1.108588829046702</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -1033,17 +1033,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
+          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5272340157221905</v>
+        <v>0.5276086138227275</v>
       </c>
       <c r="C24" t="n">
-        <v>0.003470598386898386</v>
+        <v>0.003595269992398425</v>
       </c>
       <c r="D24" t="n">
-        <v>1.07753160563651</v>
+        <v>1.107782579546674</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1052,17 +1052,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRIV_AID_BIZ_CGP_YN</t>
+          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5265017553183537</v>
+        <v>0.5273963230484093</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003403837161971784</v>
+        <v>0.003508039652314369</v>
       </c>
       <c r="D25" t="n">
-        <v>1.056803961043293</v>
+        <v>1.080904973314775</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1071,17 +1071,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PBAC_TY_DV_CD</t>
+          <t>CONT_BIZ_YN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5255392965615575</v>
+        <v>0.5263770990173797</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003395272481664479</v>
+        <v>0.003431180505697649</v>
       </c>
       <c r="D26" t="n">
-        <v>1.054144847917979</v>
+        <v>1.057222962261128</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -1090,17 +1090,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NTS_BT_CD</t>
+          <t>CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5242792993903789</v>
+        <v>0.5261580526645433</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003417323569526058</v>
+        <v>0.003480421910136889</v>
       </c>
       <c r="D27" t="n">
-        <v>1.060991143991652</v>
+        <v>1.07239533322229</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1109,17 +1109,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>PBAC_TY_DV_CD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5233797604260239</v>
+        <v>0.5258992581122339</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003979462412441149</v>
+        <v>0.003423424015914176</v>
       </c>
       <c r="D28" t="n">
-        <v>1.235520807891563</v>
+        <v>1.0548330153924</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -1128,17 +1128,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>NTS_BT_CD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5230576569651261</v>
+        <v>0.5254248477353729</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003317659290224514</v>
+        <v>0.003454149577878362</v>
       </c>
       <c r="D29" t="n">
-        <v>1.030047946615141</v>
+        <v>1.064300243823832</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1147,17 +1147,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>PRIV_AID_BIZ_CGP_YN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5225675744959367</v>
+        <v>0.5253439024666549</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003522415166320156</v>
+        <v>0.003421221114454581</v>
       </c>
       <c r="D30" t="n">
-        <v>1.093619383968923</v>
+        <v>1.054154252499333</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1166,17 +1166,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CUMU_EXE_CNT</t>
+          <t>TMNT_INDV_BZR_CLT_NUM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.522390312253299</v>
+        <v>0.5253388154346381</v>
       </c>
       <c r="C31" t="n">
-        <v>0.003442416494801953</v>
+        <v>0.003532912943437238</v>
       </c>
       <c r="D31" t="n">
-        <v>1.068781852408023</v>
+        <v>1.088568987049534</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1185,17 +1185,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CONT_BIZ_YN</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5221640910545116</v>
+        <v>0.5233817578085069</v>
       </c>
       <c r="C32" t="n">
-        <v>0.003373762866696996</v>
+        <v>0.003482533176817451</v>
       </c>
       <c r="D32" t="n">
-        <v>1.047466665262207</v>
+        <v>1.073045861403608</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -1204,17 +1204,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AID_BIZ_DV_CD</t>
+          <t>FYR</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5220846893995945</v>
+        <v>0.5211636087832021</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003374384128634491</v>
+        <v>0.003493648674309353</v>
       </c>
       <c r="D33" t="n">
-        <v>1.047659551127526</v>
+        <v>1.076470793191918</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5220721164875944</v>
+        <v>0.521159305777018</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003454045708876738</v>
+        <v>0.003481338638157068</v>
       </c>
       <c r="D34" t="n">
-        <v>1.072392424510401</v>
+        <v>1.072677797497041</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.521451849481506</v>
+        <v>0.5208445131762683</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003569181799801592</v>
+        <v>0.003563029752492529</v>
       </c>
       <c r="D35" t="n">
-        <v>1.108139221774328</v>
+        <v>1.097848645181892</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -1261,17 +1261,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TMNT_CORP_CLT_NUM</t>
+          <t>ODN_CAPT_DV_CD</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5213734759031593</v>
+        <v>0.5202024678608377</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003624816855234848</v>
+        <v>0.003381870465804889</v>
       </c>
       <c r="D36" t="n">
-        <v>1.125412476679586</v>
+        <v>1.042029443191504</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -1280,17 +1280,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ODN_CAPT_DV_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5210257416606934</v>
+        <v>0.5200161728582947</v>
       </c>
       <c r="C37" t="n">
-        <v>0.003362009453971953</v>
+        <v>0.003324221225866052</v>
       </c>
       <c r="D37" t="n">
-        <v>1.043817532670798</v>
+        <v>1.024266431272127</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -1299,17 +1299,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CARD_FR_USE_CNT</t>
+          <t>ACNT_DV_CD</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5205222146948495</v>
+        <v>0.5196067552330154</v>
       </c>
       <c r="C38" t="n">
-        <v>0.003383878629699417</v>
+        <v>0.003564583272714486</v>
       </c>
       <c r="D38" t="n">
-        <v>1.050607349701923</v>
+        <v>1.098327319284949</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -1318,17 +1318,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CARD_RTRCN_CNT</t>
+          <t>AID_BIZ_DV_CD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5199060357262425</v>
+        <v>0.5192295698731296</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003422760764030299</v>
+        <v>0.003379612163459114</v>
       </c>
       <c r="D39" t="n">
-        <v>1.062679253150704</v>
+        <v>1.041333610054274</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -1337,17 +1337,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5195471202619161</v>
+        <v>0.5170874609718751</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003522506227733464</v>
+        <v>0.003378631456029198</v>
       </c>
       <c r="D40" t="n">
-        <v>1.0936476561975</v>
+        <v>1.041031432301619</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -1356,17 +1356,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5193890098681585</v>
+        <v>0.5169179855658851</v>
       </c>
       <c r="C41" t="n">
-        <v>0.003429165411120457</v>
+        <v>0.003367512876676662</v>
       </c>
       <c r="D41" t="n">
-        <v>1.064667731474397</v>
+        <v>1.037605550923561</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -1375,17 +1375,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TMNT_EXE_CNT</t>
+          <t>TMNT_EXE_AMT</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5193318560078047</v>
+        <v>0.516696102517889</v>
       </c>
       <c r="C42" t="n">
-        <v>0.00340002232224683</v>
+        <v>0.003565527458554109</v>
       </c>
       <c r="D42" t="n">
-        <v>1.055619551349105</v>
+        <v>1.098618243924044</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -1394,17 +1394,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_CNT</t>
+          <t>INDV_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5184681382103629</v>
+        <v>0.5163873624470696</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003401948461559931</v>
+        <v>0.003440438999690085</v>
       </c>
       <c r="D43" t="n">
-        <v>1.056217568104532</v>
+        <v>1.060075710004508</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -1413,17 +1413,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_AMT</t>
+          <t>CARD_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5184118730901945</v>
+        <v>0.5159450497887964</v>
       </c>
       <c r="C44" t="n">
-        <v>0.003406167626284526</v>
+        <v>0.003370333263437088</v>
       </c>
       <c r="D44" t="n">
-        <v>1.057527510320059</v>
+        <v>1.03847457475971</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -1432,17 +1432,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>EXE_PLAN_CHG_TMS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5174884883563382</v>
+        <v>0.5158741398846266</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003350371253806113</v>
+        <v>0.003355703063720464</v>
       </c>
       <c r="D45" t="n">
-        <v>1.040204170618087</v>
+        <v>1.033966685111469</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -1451,17 +1451,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>TMNT_CORP_CLT_NUM</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5171348802274687</v>
+        <v>0.5158158233953907</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0160308013768529</v>
+        <v>0.003571445535361535</v>
       </c>
       <c r="D46" t="n">
-        <v>4.977151839996526</v>
+        <v>1.10044173490123</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -1470,17 +1470,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_DLNG_AMT</t>
+          <t>LBST_EXE_RT_DV_CD</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5164120695921558</v>
+        <v>0.5149116792408132</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003488027150197082</v>
+        <v>0.003413090430529153</v>
       </c>
       <c r="D47" t="n">
-        <v>1.082942788725973</v>
+        <v>1.051649008100044</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -1489,17 +1489,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EXE_PLAN_CHG_TMS</t>
+          <t>TMNT_EXE_CNT</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5159538181644527</v>
+        <v>0.514261549904789</v>
       </c>
       <c r="C48" t="n">
-        <v>0.003330867687137105</v>
+        <v>0.003355144383326447</v>
       </c>
       <c r="D48" t="n">
-        <v>1.034148814404061</v>
+        <v>1.033794543266952</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -1508,17 +1508,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>INDV_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5155481869342464</v>
+        <v>0.5115497224864157</v>
       </c>
       <c r="C49" t="n">
-        <v>0.003455156573530645</v>
+        <v>0.003381430773260546</v>
       </c>
       <c r="D49" t="n">
-        <v>1.0727373194365</v>
+        <v>1.041893964147647</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -1527,17 +1527,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ACNT_DV_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5152422724365169</v>
+        <v>0.5110866082275073</v>
       </c>
       <c r="C50" t="n">
-        <v>0.003436104300362244</v>
+        <v>0.01582347427300902</v>
       </c>
       <c r="D50" t="n">
-        <v>1.066822078256284</v>
+        <v>4.875564056275702</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -1546,17 +1546,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TMNT_EXE_AMT</t>
+          <t>TMNT_INDV_BZR_DLNG_AMT</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5145113246400066</v>
+        <v>0.5103821527116879</v>
       </c>
       <c r="C51" t="n">
-        <v>0.003454049901810517</v>
+        <v>0.003446195810906694</v>
       </c>
       <c r="D51" t="n">
-        <v>1.072393726308582</v>
+        <v>1.061849511469484</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1565,17 +1565,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_CNT</t>
+          <t>INDV_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5129590181439447</v>
+        <v>0.5100964982150622</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003368541332843181</v>
+        <v>0.003460614357021484</v>
       </c>
       <c r="D52" t="n">
-        <v>1.045845513192689</v>
+        <v>1.066292185939586</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -1584,17 +1584,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LBST_EXE_RT_DV_CD</t>
+          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5127959226039689</v>
+        <v>0.5097223380819718</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00336061685656902</v>
+        <v>0.003340206920701427</v>
       </c>
       <c r="D53" t="n">
-        <v>1.043385166966586</v>
+        <v>1.02919197908857</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -1603,17 +1603,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_AMT</t>
+          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5110227382293486</v>
+        <v>0.5097172996363016</v>
       </c>
       <c r="C54" t="n">
-        <v>0.003384696063587407</v>
+        <v>0.003368872853955759</v>
       </c>
       <c r="D54" t="n">
-        <v>1.050861141916301</v>
+        <v>1.038024590144968</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5103453240577478</v>
+        <v>0.5096960200622909</v>
       </c>
       <c r="C55" t="n">
-        <v>0.003442118773615348</v>
+        <v>0.003437294063891046</v>
       </c>
       <c r="D55" t="n">
-        <v>1.068689417630941</v>
+        <v>1.059106685397362</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5090919401345113</v>
+        <v>0.5088206448386565</v>
       </c>
       <c r="C56" t="n">
-        <v>0.003449496554619375</v>
+        <v>0.003483479100347937</v>
       </c>
       <c r="D56" t="n">
-        <v>1.070980029025597</v>
+        <v>1.073337321463874</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -1660,17 +1660,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_CNT</t>
+          <t>INDV_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.508955391314082</v>
+        <v>0.5087932774369425</v>
       </c>
       <c r="C57" t="n">
-        <v>0.003328207626318328</v>
+        <v>0.003324219592079169</v>
       </c>
       <c r="D57" t="n">
-        <v>1.033322933882717</v>
+        <v>1.024265927866083</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -1679,17 +1679,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>INVC_EXE_CNT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5088376001837501</v>
+        <v>0.5073025943381575</v>
       </c>
       <c r="C58" t="n">
-        <v>0.003323761544149857</v>
+        <v>0.003300668094053085</v>
       </c>
       <c r="D58" t="n">
-        <v>1.031942539632587</v>
+        <v>1.017009187957623</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -1698,17 +1698,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
+          <t>TMNT_INDV_CLT_NUM</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.508790845504105</v>
+        <v>0.5071974293985568</v>
       </c>
       <c r="C59" t="n">
-        <v>0.003291374881933087</v>
+        <v>0.003380306708912013</v>
       </c>
       <c r="D59" t="n">
-        <v>1.021887313343258</v>
+        <v>1.041547614942656</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -1717,17 +1717,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EVENT_FSTV_YN</t>
+          <t>PRIV_AID_BZR_YN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5082246071227563</v>
+        <v>0.5065540813876619</v>
       </c>
       <c r="C60" t="n">
-        <v>0.00331255169934613</v>
+        <v>0.003288455027911747</v>
       </c>
       <c r="D60" t="n">
-        <v>1.028462170911189</v>
+        <v>1.013246070878007</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5081502399885123</v>
+        <v>0.5062834035285614</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003281209816039916</v>
+        <v>0.003287188609086437</v>
       </c>
       <c r="D61" t="n">
-        <v>1.018731321623035</v>
+        <v>1.012855859095289</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -1755,17 +1755,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5081175164409926</v>
+        <v>0.5058392429280455</v>
       </c>
       <c r="C62" t="n">
-        <v>0.003134935180660066</v>
+        <v>0.003350829880802737</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9733168065585012</v>
+        <v>1.032465149161563</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -1774,17 +1774,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TMNT_INDV_CLT_NUM</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.507794831365755</v>
+        <v>0.505462729056386</v>
       </c>
       <c r="C63" t="n">
-        <v>0.003274051402958515</v>
+        <v>0.003385789540039949</v>
       </c>
       <c r="D63" t="n">
-        <v>1.016508818330655</v>
+        <v>1.043236997053865</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -1793,17 +1793,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5070155175249794</v>
+        <v>0.5050176486374277</v>
       </c>
       <c r="C64" t="n">
-        <v>0.003477346580887464</v>
+        <v>0.003311418286362922</v>
       </c>
       <c r="D64" t="n">
-        <v>1.07962674644325</v>
+        <v>1.020321561101446</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -1812,17 +1812,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>INVC_EXE_CNT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5063388201198276</v>
+        <v>0.5049399835700077</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003267519380533657</v>
+        <v>0.003255388777023212</v>
       </c>
       <c r="D65" t="n">
-        <v>1.01448079323905</v>
+        <v>1.003057624173674</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -1831,17 +1831,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CUMU_EXE_AMT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5058617515853102</v>
+        <v>0.5047469226072485</v>
       </c>
       <c r="C66" t="n">
-        <v>0.003285768557352733</v>
+        <v>0.003233363701681251</v>
       </c>
       <c r="D66" t="n">
-        <v>1.020146693642173</v>
+        <v>0.9962712090146975</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -1850,17 +1850,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TMNT_CORP_DLNG_AMT</t>
+          <t>ETI_EXE_CNT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5058241424773369</v>
+        <v>0.5043638520704046</v>
       </c>
       <c r="C67" t="n">
-        <v>0.003237579151372644</v>
+        <v>0.003293738443247539</v>
       </c>
       <c r="D67" t="n">
-        <v>1.005185121540827</v>
+        <v>1.014874008552195</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -1869,17 +1869,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PRIV_AID_BZR_YN</t>
+          <t>CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.505148853081</v>
+        <v>0.5042593457457246</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003254298073168384</v>
+        <v>0.003309959930171629</v>
       </c>
       <c r="D68" t="n">
-        <v>1.010375917086369</v>
+        <v>1.019872209150994</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -1888,17 +1888,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_AMT</t>
+          <t>EVENT_FSTV_YN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5046052679505422</v>
+        <v>0.5042373282406204</v>
       </c>
       <c r="C69" t="n">
-        <v>0.003297485575643109</v>
+        <v>0.003283236679381769</v>
       </c>
       <c r="D69" t="n">
-        <v>1.023784526696946</v>
+        <v>1.011638181732621</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
@@ -1907,17 +1907,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SBAT_EXE_SUM_AMT</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5042446612019271</v>
+        <v>0.5040854768051439</v>
       </c>
       <c r="C70" t="n">
-        <v>0.003286391102475304</v>
+        <v>0.003301821808960061</v>
       </c>
       <c r="D70" t="n">
-        <v>1.02033997790348</v>
+        <v>1.017364673158571</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -1926,17 +1926,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TMNT_DLNG_AMT</t>
+          <t>NTN_DRCT_BIZ_YN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5042446612019271</v>
+        <v>0.5040737591902528</v>
       </c>
       <c r="C71" t="n">
-        <v>0.003286391102475304</v>
+        <v>0.003292080288896853</v>
       </c>
       <c r="D71" t="n">
-        <v>1.02033997790348</v>
+        <v>1.014363094348874</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -1945,17 +1945,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ETI_EXE_CNT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5040588191017096</v>
+        <v>0.5035697165404435</v>
       </c>
       <c r="C72" t="n">
-        <v>0.003263138153769021</v>
+        <v>0.003460520950933457</v>
       </c>
       <c r="D72" t="n">
-        <v>1.013120534925044</v>
+        <v>1.066263405448175</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -1964,17 +1964,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LSA_MNG_CMMT_DLBR_YN</t>
+          <t>CB_YN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5039181044162684</v>
+        <v>0.503129107726445</v>
       </c>
       <c r="C73" t="n">
-        <v>0.003282289210406969</v>
+        <v>0.003265837539623402</v>
       </c>
       <c r="D73" t="n">
-        <v>1.019066445833845</v>
+        <v>1.006277120125517</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -1983,17 +1983,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CB_YN</t>
+          <t>CORP_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5033859038634763</v>
+        <v>0.5031060898409222</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003242767323660943</v>
+        <v>0.003332726814101617</v>
       </c>
       <c r="D74" t="n">
-        <v>1.006795915701636</v>
+        <v>1.026887192020577</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
@@ -2002,17 +2002,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AST_LAT_RT</t>
+          <t>VNCL_GOEM_VRSC_YN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5032420313050697</v>
+        <v>0.5027770286344506</v>
       </c>
       <c r="C75" t="n">
-        <v>0.003242169745757363</v>
+        <v>0.003263533460838379</v>
       </c>
       <c r="D75" t="n">
-        <v>1.006610383120175</v>
+        <v>1.005567182250101</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -2021,17 +2021,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NTN_DRCT_BIZ_YN</t>
+          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5029387252848896</v>
+        <v>0.5019247576720666</v>
       </c>
       <c r="C76" t="n">
-        <v>0.003250350701130647</v>
+        <v>0.003258027815122984</v>
       </c>
       <c r="D76" t="n">
-        <v>1.009150359515108</v>
+        <v>1.003870770457505</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -2040,17 +2040,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VNCL_GOEM_VRSC_YN</t>
+          <t>LSA_MNG_CMMT_DLBR_YN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5025320500778649</v>
+        <v>0.5018066048130083</v>
       </c>
       <c r="C77" t="n">
-        <v>0.003237220244588723</v>
+        <v>0.003264822394257026</v>
       </c>
       <c r="D77" t="n">
-        <v>1.005073690208233</v>
+        <v>1.005964331279351</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -2059,17 +2059,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
+          <t>TMNT_DLNG_AMT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5024154615084052</v>
+        <v>0.501789880728077</v>
       </c>
       <c r="C78" t="n">
-        <v>0.003275007452927767</v>
+        <v>0.003326103108533695</v>
       </c>
       <c r="D78" t="n">
-        <v>1.016805647275867</v>
+        <v>1.024846281141643</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
@@ -2078,17 +2078,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
+          <t>SBAT_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5022950669216547</v>
+        <v>0.5017894189501502</v>
       </c>
       <c r="C79" t="n">
-        <v>0.003203771771735847</v>
+        <v>0.003326097916930697</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9946887990046561</v>
+        <v>1.024844681493391</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -2097,17 +2097,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
+          <t>PBCN_DGR</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.502285083657963</v>
+        <v>0.5012132085496424</v>
       </c>
       <c r="C80" t="n">
-        <v>0.003210006618193271</v>
+        <v>0.003253334018405725</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9966245585957189</v>
+        <v>1.002424507382324</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RERE_DSCRD_CNT</t>
+          <t>AST_LAT_RT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5021200110476598</v>
+        <v>0.5008661006299149</v>
       </c>
       <c r="C81" t="n">
-        <v>0.003437055272839824</v>
+        <v>0.003250909419827864</v>
       </c>
       <c r="D81" t="n">
-        <v>1.067117330770822</v>
+        <v>1.001677434680516</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FLD_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5014156656215643</v>
+        <v>0.5008418452459913</v>
       </c>
       <c r="C82" t="n">
-        <v>0.003269976159089338</v>
+        <v>0.003115840495814372</v>
       </c>
       <c r="D82" t="n">
-        <v>1.015243559842006</v>
+        <v>0.9600596976603148</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
@@ -2154,17 +2154,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PBCN_DGR</t>
+          <t>TMNT_CORP_DLNG_AMT</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5011246228769732</v>
+        <v>0.5003170213436747</v>
       </c>
       <c r="C83" t="n">
-        <v>0.003228116227310739</v>
+        <v>0.003231417296628579</v>
       </c>
       <c r="D83" t="n">
-        <v>1.002247126814346</v>
+        <v>0.9956714783645235</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -2173,17 +2173,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
+          <t>RERE_DSCRD_CNT</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5009446002675736</v>
+        <v>0.500194525612712</v>
       </c>
       <c r="C84" t="n">
-        <v>0.003227025328135209</v>
+        <v>0.003323987596027563</v>
       </c>
       <c r="D84" t="n">
-        <v>1.001908430656175</v>
+        <v>1.024194444727115</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999098481843425</v>
+        <v>0.9999082090604214</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1910</v>
+        <v>1924</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9968807471782481</v>
+        <v>0.9968577994433535</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9967791214951432</v>
+        <v>0.9967545346363276</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">

--- a/outputs/reports/comparison/leakage_audit.xlsx
+++ b/outputs/reports/comparison/leakage_audit.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량(univariate)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="의심피처(suspects)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라벨정의검증(label_def)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="피처목록(feature_list)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그룹중복(group_overlap)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="피처목록(feature_list)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +453,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003245465363672425</v>
+        <v>0.003298540954145681</v>
       </c>
     </row>
     <row r="4">
@@ -494,6 +495,40 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>단변량 ROC-AUC가 0.9 이상이면 타겟과 거의 같이 움직이는 피처일 수 있음. 다만 여러 피처가 중정도(0.7~0.85)만으로도 앙상블 AUC 0.97대는 충분히 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>그룹중복판정(group_verdict)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PASS_그룹중복_낮음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>최대_이미양성으로본비율(group_worst_ratio)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>그룹중복_해석가이드</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Test 양성 엔티티 중 Train에서 이미 양성으로 등장한 비율이 높으면, 지표가 '신규 대상 탐지'가 아니라 '기존 대상 재탐지' 성능을 재고 있을 수 있음. 랜덤분할기대중복비율과 비슷하면 원인은 행 단위 random 분할. 시간 분할(split.mode=time, 기간 겹침 금지) 또는 사업 단위 그룹 분할로 대조 권장.</t>
         </is>
       </c>
     </row>
@@ -615,17 +650,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5953456177723242</v>
+        <v>0.6102765417449965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004388227477903696</v>
+        <v>0.005028550594959024</v>
       </c>
       <c r="D2" t="n">
-        <v>1.352110402108304</v>
+        <v>1.524477235499843</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -634,17 +669,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5865129899625758</v>
+        <v>0.5998644155237193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00451154947971646</v>
+        <v>0.00454795316016301</v>
       </c>
       <c r="D3" t="n">
-        <v>1.390108651355746</v>
+        <v>1.378777230110495</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -653,17 +688,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5665283492279621</v>
+        <v>0.5761693939467283</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003816934440223919</v>
+        <v>0.003972629328477104</v>
       </c>
       <c r="D4" t="n">
-        <v>1.176082321798328</v>
+        <v>1.204359558878362</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -672,17 +707,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5639898417659797</v>
+        <v>0.5711620781593952</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004020446872672561</v>
+        <v>0.003930160815310115</v>
       </c>
       <c r="D5" t="n">
-        <v>1.238789024734253</v>
+        <v>1.19148462000164</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -691,17 +726,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5635780338585543</v>
+        <v>0.5615620562385282</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003781455584011756</v>
+        <v>0.003990484660004932</v>
       </c>
       <c r="D6" t="n">
-        <v>1.165150497780333</v>
+        <v>1.209772658723427</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -710,17 +745,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>OPCT_YN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5598697291247227</v>
+        <v>0.5586010024042695</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003659745890894433</v>
+        <v>0.003873567996462748</v>
       </c>
       <c r="D7" t="n">
-        <v>1.127649036671039</v>
+        <v>1.174327695278229</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -729,17 +764,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.55683852371723</v>
+        <v>0.551091824190286</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005400036456637725</v>
+        <v>0.003688696469464779</v>
       </c>
       <c r="D8" t="n">
-        <v>1.663871233100231</v>
+        <v>1.118281240324981</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -748,17 +783,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_CNT</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5476144328059797</v>
+        <v>0.5504587929986074</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003792557774419537</v>
+        <v>0.005692863665587746</v>
       </c>
       <c r="D9" t="n">
-        <v>1.168571329360313</v>
+        <v>1.725873270857172</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -767,17 +802,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OPCT_YN</t>
+          <t>LBST_EXE_CNT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5464846449371249</v>
+        <v>0.549257369890192</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003663743761293497</v>
+        <v>0.003791115542932379</v>
       </c>
       <c r="D10" t="n">
-        <v>1.128880869382555</v>
+        <v>1.149331051405507</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -786,17 +821,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LBST_EXE_CNT</t>
+          <t>TMNT_CLT_NUM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5444679008528904</v>
+        <v>0.546494090338714</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00369384421156972</v>
+        <v>0.003728982782713846</v>
       </c>
       <c r="D11" t="n">
-        <v>1.138155487011554</v>
+        <v>1.1304946139981</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,17 +840,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CUMU_PYHWY_EXE_AMT</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5435407363211828</v>
+        <v>0.5445845128778724</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003560921462815187</v>
+        <v>0.00390130950783065</v>
       </c>
       <c r="D12" t="n">
-        <v>1.097199034281422</v>
+        <v>1.182737932335627</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -824,17 +859,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>CUMU_PYHWY_EXE_CNT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5420107215366481</v>
+        <v>0.5436159780519747</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00380586140159499</v>
+        <v>0.003756337315938071</v>
       </c>
       <c r="D13" t="n">
-        <v>1.172670472529229</v>
+        <v>1.138787533080958</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -847,13 +882,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5408115195586706</v>
+        <v>0.5428638312693133</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003580103909639817</v>
+        <v>0.003615649289667215</v>
       </c>
       <c r="D14" t="n">
-        <v>1.103109572424686</v>
+        <v>1.096135940080715</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -862,17 +897,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>TMNT_CORP_CLT_NUM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5396393502764638</v>
+        <v>0.5411646160592046</v>
       </c>
       <c r="C15" t="n">
-        <v>0.004214741324079186</v>
+        <v>0.003947984377281862</v>
       </c>
       <c r="D15" t="n">
-        <v>1.29865546286711</v>
+        <v>1.196888088450121</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -885,13 +920,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5392026379213561</v>
+        <v>0.5399526557139638</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003522438628760229</v>
+        <v>0.003632431637654578</v>
       </c>
       <c r="D16" t="n">
-        <v>1.085341617934999</v>
+        <v>1.101223749576083</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -900,17 +935,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AID_BIZ_EXE_TY_CD</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5368930610192355</v>
+        <v>0.5397321452784584</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003517556737091153</v>
+        <v>0.003596629212680411</v>
       </c>
       <c r="D17" t="n">
-        <v>1.083837398625275</v>
+        <v>1.090369730944248</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -919,17 +954,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5362428540281104</v>
+        <v>0.5375056812269929</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003583608447263103</v>
+        <v>0.003735201711269473</v>
       </c>
       <c r="D18" t="n">
-        <v>1.104189398345035</v>
+        <v>1.132379971385526</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -938,17 +973,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LBST_EXE_AVG_AMT</t>
+          <t>TMNT_INDV_BZR_CLT_NUM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5339217389068401</v>
+        <v>0.5367795722044035</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003611332294837258</v>
+        <v>0.00364203013711108</v>
       </c>
       <c r="D19" t="n">
-        <v>1.112731731868133</v>
+        <v>1.104133672354043</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -957,17 +992,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LODI_CNT</t>
+          <t>ETC_EXE_CNT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5325959425035319</v>
+        <v>0.5362190782905764</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003522441688832761</v>
+        <v>0.003673514521931621</v>
       </c>
       <c r="D20" t="n">
-        <v>1.085342560811348</v>
+        <v>1.113678615181256</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -976,17 +1011,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TMNT_CLT_NUM</t>
+          <t>LODI_CNT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5323037213752917</v>
+        <v>0.5347050272341033</v>
       </c>
       <c r="C21" t="n">
-        <v>0.003614848678399931</v>
+        <v>0.003602585244128015</v>
       </c>
       <c r="D21" t="n">
-        <v>1.11381520778565</v>
+        <v>1.092175387302742</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -995,17 +1030,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AID_BIZ_DPI_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5292940530079201</v>
+        <v>0.5344274074045279</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003447784372087854</v>
+        <v>0.00411741339066379</v>
       </c>
       <c r="D22" t="n">
-        <v>1.062338982470759</v>
+        <v>1.248252923914415</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -1014,17 +1049,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5283204087837603</v>
+        <v>0.5316615690560564</v>
       </c>
       <c r="C23" t="n">
-        <v>0.003597886647225243</v>
+        <v>0.003575825378118196</v>
       </c>
       <c r="D23" t="n">
-        <v>1.108588829046702</v>
+        <v>1.084062750115022</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -1033,17 +1068,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>AID_BIZ_DPI_DV_CD</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5276086138227275</v>
+        <v>0.5312885510365969</v>
       </c>
       <c r="C24" t="n">
-        <v>0.003595269992398425</v>
+        <v>0.003519091765955575</v>
       </c>
       <c r="D24" t="n">
-        <v>1.107782579546674</v>
+        <v>1.066863141878745</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -1052,17 +1087,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
+          <t>TMNT_CORP_DLNG_AMT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5273963230484093</v>
+        <v>0.5267355860777962</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003508039652314369</v>
+        <v>0.003541232479017544</v>
       </c>
       <c r="D25" t="n">
-        <v>1.080904973314775</v>
+        <v>1.073575416599525</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -1071,17 +1106,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONT_BIZ_YN</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5263770990173797</v>
+        <v>0.5262871650099309</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003431180505697649</v>
+        <v>0.003538900491734144</v>
       </c>
       <c r="D26" t="n">
-        <v>1.057222962261128</v>
+        <v>1.072868441207733</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -1094,13 +1129,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5261580526645433</v>
+        <v>0.5256072341678238</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003480421910136889</v>
+        <v>0.003510008630121882</v>
       </c>
       <c r="D27" t="n">
-        <v>1.07239533322229</v>
+        <v>1.064109458974709</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -1109,17 +1144,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PBAC_TY_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5258992581122339</v>
+        <v>0.5252018201778955</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003423424015914176</v>
+        <v>0.003800308173116553</v>
       </c>
       <c r="D28" t="n">
-        <v>1.0548330153924</v>
+        <v>1.152117929092328</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -1132,13 +1167,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5254248477353729</v>
+        <v>0.5250593577702061</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003454149577878362</v>
+        <v>0.003510376875017002</v>
       </c>
       <c r="D29" t="n">
-        <v>1.064300243823832</v>
+        <v>1.064221097696265</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1147,17 +1182,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PRIV_AID_BIZ_CGP_YN</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5253439024666549</v>
+        <v>0.5250466200090056</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003421221114454581</v>
+        <v>0.003613490121119549</v>
       </c>
       <c r="D30" t="n">
-        <v>1.054154252499333</v>
+        <v>1.095481357167336</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1166,17 +1201,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>CONT_BIZ_YN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5253388154346381</v>
+        <v>0.5248718769511289</v>
       </c>
       <c r="C31" t="n">
-        <v>0.003532912943437238</v>
+        <v>0.003475701110872133</v>
       </c>
       <c r="D31" t="n">
-        <v>1.088568987049534</v>
+        <v>1.053708642454111</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1185,17 +1220,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>TMNT_EXE_CNT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5233817578085069</v>
+        <v>0.5247734201062337</v>
       </c>
       <c r="C32" t="n">
-        <v>0.003482533176817451</v>
+        <v>0.003494915553477982</v>
       </c>
       <c r="D32" t="n">
-        <v>1.073045861403608</v>
+        <v>1.059533776315705</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -1204,17 +1239,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5211636087832021</v>
+        <v>0.5244998927102782</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003493648674309353</v>
+        <v>0.003539452500957447</v>
       </c>
       <c r="D33" t="n">
-        <v>1.076470793191918</v>
+        <v>1.073035790721041</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1223,17 +1258,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETC_EXE_CNT</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.521159305777018</v>
+        <v>0.5242186117695593</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003481338638157068</v>
+        <v>0.003738662492270207</v>
       </c>
       <c r="D34" t="n">
-        <v>1.072677797497041</v>
+        <v>1.133429156782598</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -1242,17 +1277,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>CORP_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5208445131762683</v>
+        <v>0.5239794018015742</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003563029752492529</v>
+        <v>0.003563216986361382</v>
       </c>
       <c r="D35" t="n">
-        <v>1.097848645181892</v>
+        <v>1.080240335316453</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -1261,17 +1296,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ODN_CAPT_DV_CD</t>
+          <t>PRIV_AID_BIZ_CGP_YN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5202024678608377</v>
+        <v>0.5232060332143686</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003381870465804889</v>
+        <v>0.003461165180058938</v>
       </c>
       <c r="D36" t="n">
-        <v>1.042029443191504</v>
+        <v>1.049301866544621</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -1280,17 +1315,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>TMNT_EXE_AMT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5200161728582947</v>
+        <v>0.5228311905900279</v>
       </c>
       <c r="C37" t="n">
-        <v>0.003324221225866052</v>
+        <v>0.003590374328599662</v>
       </c>
       <c r="D37" t="n">
-        <v>1.024266431272127</v>
+        <v>1.088473473123684</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -1299,17 +1334,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ACNT_DV_CD</t>
+          <t>INDV_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5196067552330154</v>
+        <v>0.5225820716960751</v>
       </c>
       <c r="C38" t="n">
-        <v>0.003564583272714486</v>
+        <v>0.003513001674533521</v>
       </c>
       <c r="D38" t="n">
-        <v>1.098327319284949</v>
+        <v>1.065016843316225</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -1318,17 +1353,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AID_BIZ_DV_CD</t>
+          <t>INDV_BZR_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5192295698731296</v>
+        <v>0.5223263147040678</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003379612163459114</v>
+        <v>0.0034818484595543</v>
       </c>
       <c r="D39" t="n">
-        <v>1.041333610054274</v>
+        <v>1.055572299376254</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -1337,17 +1372,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CARD_FR_USE_CNT</t>
+          <t>INDV_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5170874609718751</v>
+        <v>0.5221836487417177</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003378631456029198</v>
+        <v>0.003460881981067638</v>
       </c>
       <c r="D40" t="n">
-        <v>1.041031432301619</v>
+        <v>1.04921601070859</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -1356,17 +1391,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>PBAC_TY_DV_CD</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5169179855658851</v>
+        <v>0.5221449446287328</v>
       </c>
       <c r="C41" t="n">
-        <v>0.003367512876676662</v>
+        <v>0.003451246101084407</v>
       </c>
       <c r="D41" t="n">
-        <v>1.037605550923561</v>
+        <v>1.046294755487817</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -1375,17 +1410,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TMNT_EXE_AMT</t>
+          <t>AID_BIZ_DV_CD</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.516696102517889</v>
+        <v>0.5214768728975676</v>
       </c>
       <c r="C42" t="n">
-        <v>0.003565527458554109</v>
+        <v>0.003450561736219478</v>
       </c>
       <c r="D42" t="n">
-        <v>1.098618243924044</v>
+        <v>1.046087280463422</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -1394,17 +1429,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_AMT</t>
+          <t>ODN_CAPT_DV_CD</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5163873624470696</v>
+        <v>0.5211339050452704</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003440438999690085</v>
+        <v>0.003443838891536111</v>
       </c>
       <c r="D43" t="n">
-        <v>1.060075710004508</v>
+        <v>1.044049153674389</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -1413,17 +1448,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CARD_RTRCN_CNT</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5159450497887964</v>
+        <v>0.5207652979239803</v>
       </c>
       <c r="C44" t="n">
-        <v>0.003370333263437088</v>
+        <v>0.003585919085862689</v>
       </c>
       <c r="D44" t="n">
-        <v>1.03847457475971</v>
+        <v>1.087122802388075</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -1432,17 +1467,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EXE_PLAN_CHG_TMS</t>
+          <t>TMNT_INDV_BZR_DLNG_AMT</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5158741398846266</v>
+        <v>0.5203631522996103</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003355703063720464</v>
+        <v>0.00362609780539213</v>
       </c>
       <c r="D45" t="n">
-        <v>1.033966685111469</v>
+        <v>1.099303557481913</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -1451,17 +1486,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TMNT_CORP_CLT_NUM</t>
+          <t>INDV_CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5158158233953907</v>
+        <v>0.52036040061816</v>
       </c>
       <c r="C46" t="n">
-        <v>0.003571445535361535</v>
+        <v>0.003533804053500495</v>
       </c>
       <c r="D46" t="n">
-        <v>1.10044173490123</v>
+        <v>1.071323382860877</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -1470,17 +1505,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LBST_EXE_RT_DV_CD</t>
+          <t>TMNT_INDV_DLNG_AMT</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5149116792408132</v>
+        <v>0.5195868666427925</v>
       </c>
       <c r="C47" t="n">
-        <v>0.003413090430529153</v>
+        <v>0.003393201899416258</v>
       </c>
       <c r="D47" t="n">
-        <v>1.051649008100044</v>
+        <v>1.02869782324564</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -1489,17 +1524,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TMNT_EXE_CNT</t>
+          <t>AID_BIZ_EXE_TY_CD</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.514261549904789</v>
+        <v>0.5184749172986963</v>
       </c>
       <c r="C48" t="n">
-        <v>0.003355144383326447</v>
+        <v>0.003427304778271853</v>
       </c>
       <c r="D48" t="n">
-        <v>1.033794543266952</v>
+        <v>1.039036600095669</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -1508,17 +1543,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_CNT</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5115497224864157</v>
+        <v>0.5181296491966558</v>
       </c>
       <c r="C49" t="n">
-        <v>0.003381430773260546</v>
+        <v>0.003430482669280371</v>
       </c>
       <c r="D49" t="n">
-        <v>1.041893964147647</v>
+        <v>1.040000023334215</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -1527,17 +1562,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>ACNT_DV_CD</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5110866082275073</v>
+        <v>0.5172478618979596</v>
       </c>
       <c r="C50" t="n">
-        <v>0.01582347427300902</v>
+        <v>0.003553241500796928</v>
       </c>
       <c r="D50" t="n">
-        <v>4.875564056275702</v>
+        <v>1.077216123792895</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -1546,17 +1581,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_DLNG_AMT</t>
+          <t>CUMU_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5103821527116879</v>
+        <v>0.5167220752849407</v>
       </c>
       <c r="C51" t="n">
-        <v>0.003446195810906694</v>
+        <v>0.003529509827033251</v>
       </c>
       <c r="D51" t="n">
-        <v>1.061849511469484</v>
+        <v>1.070021526516833</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1565,17 +1600,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>INDV_CUMU_EXE_AMT</t>
+          <t>CUMU_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5100964982150622</v>
+        <v>0.5166966239756949</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003460614357021484</v>
+        <v>0.00352439984533589</v>
       </c>
       <c r="D52" t="n">
-        <v>1.066292185939586</v>
+        <v>1.068472362274703</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -1584,17 +1619,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
+          <t>EXE_PLAN_CHG_TMS</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5097223380819718</v>
+        <v>0.5158356021251265</v>
       </c>
       <c r="C53" t="n">
-        <v>0.003340206920701427</v>
+        <v>0.003409795449209062</v>
       </c>
       <c r="D53" t="n">
-        <v>1.02919197908857</v>
+        <v>1.033728395860465</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -1603,17 +1638,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
+          <t>FYR</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5097172996363016</v>
+        <v>0.5154195072610115</v>
       </c>
       <c r="C54" t="n">
-        <v>0.003368872853955759</v>
+        <v>0.003507990513204805</v>
       </c>
       <c r="D54" t="n">
-        <v>1.038024590144968</v>
+        <v>1.063497637886194</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -1622,17 +1657,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5096960200622909</v>
+        <v>0.5145462639229582</v>
       </c>
       <c r="C55" t="n">
-        <v>0.003437294063891046</v>
+        <v>0.00341192188332316</v>
       </c>
       <c r="D55" t="n">
-        <v>1.059106685397362</v>
+        <v>1.03437305486081</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1641,17 +1676,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
+          <t>CARD_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5088206448386565</v>
+        <v>0.5141839169282661</v>
       </c>
       <c r="C56" t="n">
-        <v>0.003483479100347937</v>
+        <v>0.00343765556717192</v>
       </c>
       <c r="D56" t="n">
-        <v>1.073337321463874</v>
+        <v>1.042174590208254</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -1660,17 +1695,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INDV_BZR_CUMU_EXE_CNT</t>
+          <t>LBST_EXE_RT_DV_CD</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5087932774369425</v>
+        <v>0.5141152681189816</v>
       </c>
       <c r="C57" t="n">
-        <v>0.003324219592079169</v>
+        <v>0.003456164864275467</v>
       </c>
       <c r="D57" t="n">
-        <v>1.024265927866083</v>
+        <v>1.047785949097185</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -1679,17 +1714,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INVC_EXE_CNT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5073025943381575</v>
+        <v>0.5139523525718271</v>
       </c>
       <c r="C58" t="n">
-        <v>0.003300668094053085</v>
+        <v>0.003616307592596751</v>
       </c>
       <c r="D58" t="n">
-        <v>1.017009187957623</v>
+        <v>1.096335514055599</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -1702,13 +1737,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5071974293985568</v>
+        <v>0.5137048243590526</v>
       </c>
       <c r="C59" t="n">
-        <v>0.003380306708912013</v>
+        <v>0.003328432872420129</v>
       </c>
       <c r="D59" t="n">
-        <v>1.041547614942656</v>
+        <v>1.009062163753607</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -1717,17 +1752,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PRIV_AID_BZR_YN</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5065540813876619</v>
+        <v>0.5134020384429917</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003288455027911747</v>
+        <v>0.00366600489520257</v>
       </c>
       <c r="D60" t="n">
-        <v>1.013246070878007</v>
+        <v>1.11140196413055</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -1736,17 +1771,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TMNT_INDV_DLNG_AMT</t>
+          <t>SBAT_BDTR_CEK_CARD_EXE_CNT</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5062834035285614</v>
+        <v>0.5123333600591847</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003287188609086437</v>
+        <v>0.003511554944411213</v>
       </c>
       <c r="D61" t="n">
-        <v>1.012855859095289</v>
+        <v>1.064578246329733</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -1755,17 +1790,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FLD_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5058392429280455</v>
+        <v>0.5122030809724812</v>
       </c>
       <c r="C62" t="n">
-        <v>0.003350829880802737</v>
+        <v>0.00324356746140329</v>
       </c>
       <c r="D62" t="n">
-        <v>1.032465149161563</v>
+        <v>0.9833339972107065</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -1774,17 +1809,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>ETI_EXE_CNT</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.505462729056386</v>
+        <v>0.5111914537070147</v>
       </c>
       <c r="C63" t="n">
-        <v>0.003385789540039949</v>
+        <v>0.00342028045020009</v>
       </c>
       <c r="D63" t="n">
-        <v>1.043236997053865</v>
+        <v>1.036907074293379</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -1793,17 +1828,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
+          <t>PRIV_AID_BZR_YN</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5050176486374277</v>
+        <v>0.5108458215868614</v>
       </c>
       <c r="C64" t="n">
-        <v>0.003311418286362922</v>
+        <v>0.003371485541423886</v>
       </c>
       <c r="D64" t="n">
-        <v>1.020321561101446</v>
+        <v>1.022114197850576</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -1812,17 +1847,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5049399835700077</v>
+        <v>0.5096798481792161</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003255388777023212</v>
+        <v>0.003309172958254548</v>
       </c>
       <c r="D65" t="n">
-        <v>1.003057624173674</v>
+        <v>1.003223244536498</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -1831,17 +1866,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
+          <t>TMNT_DLNG_AMT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5047469226072485</v>
+        <v>0.5080576463975297</v>
       </c>
       <c r="C66" t="n">
-        <v>0.003233363701681251</v>
+        <v>0.003462298007492507</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9962712090146975</v>
+        <v>1.049645299428831</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -1850,17 +1885,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ETI_EXE_CNT</t>
+          <t>SBAT_EXE_SUM_AMT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5043638520704046</v>
+        <v>0.5080572093295588</v>
       </c>
       <c r="C67" t="n">
-        <v>0.003293738443247539</v>
+        <v>0.003462293137727503</v>
       </c>
       <c r="D67" t="n">
-        <v>1.014874008552195</v>
+        <v>1.049643823089725</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
@@ -1869,17 +1904,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CUMU_EXE_AMT</t>
+          <t>TMNT_SBAT_EXE_RTRCN_CNT</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5042593457457246</v>
+        <v>0.5079414741412761</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003309959930171629</v>
+        <v>0.003383854859123062</v>
       </c>
       <c r="D68" t="n">
-        <v>1.019872209150994</v>
+        <v>1.025864133919622</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -1888,17 +1923,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EVENT_FSTV_YN</t>
+          <t>TMNT_SBAT_EXE_RTRCN_SUM_AMT</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5042373282406204</v>
+        <v>0.507843981718664</v>
       </c>
       <c r="C69" t="n">
-        <v>0.003283236679381769</v>
+        <v>0.00336021106630494</v>
       </c>
       <c r="D69" t="n">
-        <v>1.011638181732621</v>
+        <v>1.018696179012648</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
@@ -1907,17 +1942,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_CNT</t>
+          <t>PBCN_DGR</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5040854768051439</v>
+        <v>0.5063179000072006</v>
       </c>
       <c r="C70" t="n">
-        <v>0.003301821808960061</v>
+        <v>0.003340617298244728</v>
       </c>
       <c r="D70" t="n">
-        <v>1.017364673158571</v>
+        <v>1.012756047199039</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
@@ -1926,17 +1961,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NTN_DRCT_BIZ_YN</t>
+          <t>VNCL_GOEM_VRSC_YN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5040737591902528</v>
+        <v>0.5036531281892829</v>
       </c>
       <c r="C71" t="n">
-        <v>0.003292080288896853</v>
+        <v>0.003322739254964285</v>
       </c>
       <c r="D71" t="n">
-        <v>1.014363094348874</v>
+        <v>1.007336061960423</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
@@ -1945,17 +1980,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>EVENT_FSTV_YN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5035697165404435</v>
+        <v>0.5032134796706612</v>
       </c>
       <c r="C72" t="n">
-        <v>0.003460520950933457</v>
+        <v>0.003325691938189675</v>
       </c>
       <c r="D72" t="n">
-        <v>1.066263405448175</v>
+        <v>1.008231210229441</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
@@ -1968,13 +2003,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.503129107726445</v>
+        <v>0.5028787520885858</v>
       </c>
       <c r="C73" t="n">
-        <v>0.003265837539623402</v>
+        <v>0.003317579142632282</v>
       </c>
       <c r="D73" t="n">
-        <v>1.006277120125517</v>
+        <v>1.005771699897396</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
@@ -1983,17 +2018,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CORP_BZR_CUMU_EXE_AMT</t>
+          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5031060898409222</v>
+        <v>0.5026470395804683</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003332726814101617</v>
+        <v>0.00331471214409166</v>
       </c>
       <c r="D74" t="n">
-        <v>1.026887192020577</v>
+        <v>1.004902528169509</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
@@ -2002,17 +2037,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VNCL_GOEM_VRSC_YN</t>
+          <t>INVC_EXE_CNT</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5027770286344506</v>
+        <v>0.5026115110843458</v>
       </c>
       <c r="C75" t="n">
-        <v>0.003263533460838379</v>
+        <v>0.003315810374828015</v>
       </c>
       <c r="D75" t="n">
-        <v>1.005567182250101</v>
+        <v>1.005235472568752</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
@@ -2021,17 +2056,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LTST_Y1_WTHN_OPBIZ_CLT_CNT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5019247576720666</v>
+        <v>0.5024915332588026</v>
       </c>
       <c r="C76" t="n">
-        <v>0.003258027815122984</v>
+        <v>0.01795364480224983</v>
       </c>
       <c r="D76" t="n">
-        <v>1.003870770457505</v>
+        <v>5.442904924277287</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
@@ -2040,17 +2075,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LSA_MNG_CMMT_DLBR_YN</t>
+          <t>NTN_DRCT_BIZ_YN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5018066048130083</v>
+        <v>0.502398116033327</v>
       </c>
       <c r="C77" t="n">
-        <v>0.003264822394257026</v>
+        <v>0.003321382007854289</v>
       </c>
       <c r="D77" t="n">
-        <v>1.005964331279351</v>
+        <v>1.006924593032535</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
@@ -2059,17 +2094,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TMNT_DLNG_AMT</t>
+          <t>LSA_MNG_CMMT_DLBR_YN</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.501789880728077</v>
+        <v>0.5022441737173295</v>
       </c>
       <c r="C78" t="n">
-        <v>0.003326103108533695</v>
+        <v>0.003325328633408133</v>
       </c>
       <c r="D78" t="n">
-        <v>1.024846281141643</v>
+        <v>1.008121069174171</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
@@ -2078,17 +2113,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SBAT_EXE_SUM_AMT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AVG_AMT</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5017894189501502</v>
+        <v>0.5021873396966008</v>
       </c>
       <c r="C79" t="n">
-        <v>0.003326097916930697</v>
+        <v>0.0033676944970224</v>
       </c>
       <c r="D79" t="n">
-        <v>1.024844681493391</v>
+        <v>1.02096488836672</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
@@ -2097,17 +2132,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PBCN_DGR</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_CNT</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5012132085496424</v>
+        <v>0.5018453042559747</v>
       </c>
       <c r="C80" t="n">
-        <v>0.003253334018405725</v>
+        <v>0.003272532201537704</v>
       </c>
       <c r="D80" t="n">
-        <v>1.002424507382324</v>
+        <v>0.9921150736129897</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
@@ -2116,17 +2151,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AST_LAT_RT</t>
+          <t>PRTC_MNPW_N_LBST_GIVE_AMT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5008661006299149</v>
+        <v>0.5018311658253051</v>
       </c>
       <c r="C81" t="n">
-        <v>0.003250909419827864</v>
+        <v>0.003276667216109198</v>
       </c>
       <c r="D81" t="n">
-        <v>1.001677434680516</v>
+        <v>0.9933686625873202</v>
       </c>
       <c r="E81" t="b">
         <v>0</v>
@@ -2135,17 +2170,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RERE_DSCRD_CNT</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5008418452459913</v>
+        <v>0.5009437787214805</v>
       </c>
       <c r="C82" t="n">
-        <v>0.003115840495814372</v>
+        <v>0.003529829313621818</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9600596976603148</v>
+        <v>1.070118383458434</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
@@ -2154,17 +2189,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TMNT_CORP_DLNG_AMT</t>
+          <t>CUMU_EXE_AMT</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5003170213436747</v>
+        <v>0.5002495149226776</v>
       </c>
       <c r="C83" t="n">
-        <v>0.003231417296628579</v>
+        <v>0.003272426984630141</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9956714783645235</v>
+        <v>0.9920831755983748</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -2173,17 +2208,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RERE_DSCRD_CNT</t>
+          <t>AST_LAT_RT</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.500194525612712</v>
+        <v>0.5002031024081002</v>
       </c>
       <c r="C84" t="n">
-        <v>0.003323987596027563</v>
+        <v>0.003288177943345881</v>
       </c>
       <c r="D84" t="n">
-        <v>1.024194444727115</v>
+        <v>0.9968583046432163</v>
       </c>
       <c r="E84" t="b">
         <v>0</v>
@@ -2278,13 +2313,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999082090604214</v>
+        <v>0.9999227931151171</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1924</v>
+        <v>1961</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2299,13 +2334,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9968577994433535</v>
+        <v>0.9967901648284857</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2320,7 +2355,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9967545346363276</v>
+        <v>0.9967014590458543</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
@@ -2343,6 +2378,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>그룹키(group_key)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>전체행수(n_rows)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Train행수(n_rows_train)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Test행수(n_rows_test)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>엔티티수(n_entities)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Train엔티티수(n_entities_train)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Test엔티티수(n_entities_test)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>엔티티당평균행수(rows_per_entity_mean)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>엔티티당최대행수(rows_per_entity_max)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>양성행수(n_pos_rows)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Test양성행수(n_pos_rows_test)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>양성엔티티수(n_pos_entities)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Train양성엔티티수(n_pos_entities_train)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Test양성엔티티수(n_pos_entities_test)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>양성엔티티당양성행수(pos_rows_per_pos_entity)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>라벨고착성(label_stickiness)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Test엔티티_Train중복비율(entity_overlap_ratio)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Test양성엔티티_Train등장비율(pos_entity_seen_ratio)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Test양성엔티티_Train에서이미양성비율(pos_entity_seen_positive_ratio)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Test양성행_이미양성엔티티비율(pos_row_seen_positive_ratio)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>랜덤분할기대중복비율(expected_overlap_under_random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PFM_BIZ_ID</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>871546</v>
+      </c>
+      <c r="C2" t="n">
+        <v>608754</v>
+      </c>
+      <c r="D2" t="n">
+        <v>262792</v>
+      </c>
+      <c r="E2" t="n">
+        <v>235378</v>
+      </c>
+      <c r="F2" t="n">
+        <v>164766</v>
+      </c>
+      <c r="G2" t="n">
+        <v>70614</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.702750469457639</v>
+      </c>
+      <c r="I2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K2" t="n">
+        <v>821</v>
+      </c>
+      <c r="L2" t="n">
+        <v>729</v>
+      </c>
+      <c r="M2" t="n">
+        <v>510</v>
+      </c>
+      <c r="N2" t="n">
+        <v>219</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.880658436213992</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8864929042912582</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.832299543999774e-05</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.894129845232883</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PFM_BIZ_ID+INST_ID</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>871546</v>
+      </c>
+      <c r="C3" t="n">
+        <v>608754</v>
+      </c>
+      <c r="D3" t="n">
+        <v>262792</v>
+      </c>
+      <c r="E3" t="n">
+        <v>235380</v>
+      </c>
+      <c r="F3" t="n">
+        <v>164766</v>
+      </c>
+      <c r="G3" t="n">
+        <v>70614</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.70271900756224</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K3" t="n">
+        <v>821</v>
+      </c>
+      <c r="L3" t="n">
+        <v>729</v>
+      </c>
+      <c r="M3" t="n">
+        <v>510</v>
+      </c>
+      <c r="N3" t="n">
+        <v>219</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.880658436213992</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8864929042912582</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.894129845232883</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
